--- a/src/attributions/attributions_saliency_traj_19.xlsx
+++ b/src/attributions/attributions_saliency_traj_19.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01406642515212297</v>
+        <v>0.0001013310175039805</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00343061238527298</v>
+        <v>1.834105205489323e-05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03312746435403824</v>
+        <v>4.493288361118175e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005429336801171303</v>
+        <v>3.643838135758415e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0597386434674263</v>
+        <v>3.496398130664602e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01028730254620314</v>
+        <v>1.357389555778354e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02580848522484303</v>
+        <v>1.038231312122662e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006972978822886944</v>
+        <v>5.349734692572383e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007973533123731613</v>
+        <v>4.697959866462043e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04186651855707169</v>
+        <v>0.0001010040723485872</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001690820790827274</v>
+        <v>2.492288331268355e-06</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04181922227144241</v>
+        <v>3.376235326868482e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03831622377038002</v>
+        <v>1.675345629337244e-05</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00609666109085083</v>
+        <v>4.342204556451179e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01016432512551546</v>
+        <v>1.577127136442869e-06</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02060693688690662</v>
+        <v>1.180216167995241e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001674637082032859</v>
+        <v>2.865130227291957e-06</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05269799381494522</v>
+        <v>6.695068805129267e-06</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01513845752924681</v>
+        <v>1.705623799352907e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01581475883722305</v>
+        <v>1.539369441161398e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0149571318179369</v>
+        <v>1.177392095996765e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01675005629658699</v>
+        <v>3.962118626077427e-06</v>
       </c>
       <c r="W3" t="n">
-        <v>0.008837507106363773</v>
+        <v>8.796241672826e-06</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03866780549287796</v>
+        <v>1.557609357405454e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01456938032060862</v>
+        <v>3.487552930891979e-06</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01937949098646641</v>
+        <v>1.363665705866879e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004693183116614819</v>
+        <v>3.867862233164487e-06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01292063668370247</v>
+        <v>7.22831828170456e-07</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03317683190107346</v>
+        <v>1.215949964716856e-06</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.009674424305558205</v>
+        <v>4.00122053179075e-06</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.006793319713324308</v>
+        <v>3.759168248507194e-05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.07514737546443939</v>
+        <v>2.790522376017179e-05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0005838721990585327</v>
+        <v>4.837678352487274e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.02048646472394466</v>
+        <v>7.757351340842433e-06</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.001893126405775547</v>
+        <v>7.664238182769623e-06</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.03313007578253746</v>
+        <v>4.130769411858637e-06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01514780055731535</v>
+        <v>7.192712928372202e-06</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0004833564744330943</v>
+        <v>2.554948150645941e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01855923235416412</v>
+        <v>2.595079058664851e-05</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0380721278488636</v>
+        <v>3.08556882373523e-05</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.005684696603566408</v>
+        <v>1.831346594372008e-07</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.007234157994389534</v>
+        <v>9.981569064620999e-07</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.01152916438877583</v>
+        <v>1.920017894008197e-06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.01312004961073399</v>
+        <v>9.17938905331539e-06</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.006382687482982874</v>
+        <v>4.565323251881637e-06</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.00648793950676918</v>
+        <v>4.471726788324304e-05</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.005779638886451721</v>
+        <v>1.64729353855364e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.01682912558317184</v>
+        <v>1.261440047528595e-05</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.03247847408056259</v>
+        <v>2.274671533086803e-05</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.06864179670810699</v>
+        <v>3.052796819247305e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.003842452308163047</v>
+        <v>1.763054387993179e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.04471495747566223</v>
+        <v>8.57553277455736e-06</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.03068393468856812</v>
+        <v>4.395230462250765e-06</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.04757111892104149</v>
+        <v>9.715347005112562e-06</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.02701771631836891</v>
+        <v>3.040525189135224e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0005252743139863014</v>
+        <v>7.766042472212575e-06</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0172102227807045</v>
+        <v>2.074847725452855e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.009733455255627632</v>
+        <v>1.765951674315147e-05</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.01844650506973267</v>
+        <v>2.952005706902128e-05</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.01145625673234463</v>
+        <v>1.77356355379743e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.02104604244232178</v>
+        <v>9.733694241731428e-06</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01522180438041687</v>
+        <v>1.450842501071747e-05</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.05561098456382751</v>
+        <v>1.666531170485541e-05</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.02858002297580242</v>
+        <v>3.323332930449396e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.02042623981833458</v>
+        <v>1.687083386059385e-05</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.003962548915296793</v>
+        <v>6.007629963278305e-06</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.02474894933402538</v>
+        <v>1.720674663374666e-05</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.04114437475800514</v>
+        <v>9.052393579622731e-06</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.002368049696087837</v>
+        <v>5.01446311318432e-06</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.000339999794960022</v>
+        <v>2.200762082793517e-06</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.02100360207259655</v>
+        <v>1.222014702761953e-07</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.008063124492764473</v>
+        <v>5.473129021993373e-06</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.01528972387313843</v>
+        <v>1.609344690223224e-05</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.01905453391373158</v>
+        <v>9.76413139142096e-06</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.006501424126327038</v>
+        <v>3.196075340383686e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.01096262875944376</v>
+        <v>6.670243237749673e-07</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.01195421162992716</v>
+        <v>1.703677662590053e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0307301077991724</v>
+        <v>6.978390047152061e-06</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.01671059057116508</v>
+        <v>5.741037512052571e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.03804488480091095</v>
+        <v>1.854192123573739e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.01822278834879398</v>
+        <v>1.389833232678939e-05</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.003329210914671421</v>
+        <v>2.374614814470988e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0009352764463983476</v>
+        <v>1.438898834749125e-06</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.002241446869447827</v>
+        <v>6.654548542428529e-06</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.003553661052137613</v>
+        <v>9.981121365854051e-06</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.002496866043657064</v>
+        <v>2.379594889134751e-06</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.004348646383732557</v>
+        <v>7.96790914137091e-07</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.00034397526178509</v>
+        <v>9.609265362087172e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.002558143110945821</v>
+        <v>3.729931449925061e-06</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.002229115692898631</v>
+        <v>1.952796537807444e-06</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.00739135080948472</v>
+        <v>1.868259641923942e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01518412493169308</v>
+        <v>3.001986442541238e-05</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.006552913226187229</v>
+        <v>1.76337798620807e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.02426990866661072</v>
+        <v>4.419068318384234e-06</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.01796363107860088</v>
+        <v>2.595007208583411e-05</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.001029607839882374</v>
+        <v>1.779944977897685e-05</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.005906431935727596</v>
+        <v>1.829058055591304e-05</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0002393736504018307</v>
+        <v>1.161179716291372e-05</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.01681811921298504</v>
+        <v>6.650432624155656e-06</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.003167633432894945</v>
+        <v>2.087786197080277e-05</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.002895754994824529</v>
+        <v>9.57440170168411e-06</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.001910661347210407</v>
+        <v>1.217173758050194e-05</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.007578564342111349</v>
+        <v>1.216373766510515e-05</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.009400330483913422</v>
+        <v>1.105706724047195e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.01278892252594233</v>
+        <v>1.836076762629091e-06</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0001202602288685739</v>
+        <v>5.214838438405422e-06</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.007828451693058014</v>
+        <v>1.814150039081142e-07</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.001878338633105159</v>
+        <v>2.024678451562067e-06</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.01895066723227501</v>
+        <v>1.87180339707993e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.0479082316160202</v>
+        <v>8.805288962321356e-05</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.02826729416847229</v>
+        <v>1.4962794011808e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.02911680564284325</v>
+        <v>4.535657717497088e-05</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.02557661570608616</v>
+        <v>1.780019920261111e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.0778132751584053</v>
+        <v>4.663258005166426e-05</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.02536126039922237</v>
+        <v>1.649193109187763e-05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.006719470024108887</v>
+        <v>2.345693064853549e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.01174537185579538</v>
+        <v>1.557482391945086e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.0176710095256567</v>
+        <v>2.417995347059332e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.002334451070055366</v>
+        <v>1.519213947176468e-05</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.02009084448218346</v>
+        <v>2.101446079905145e-05</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.02229492552578449</v>
+        <v>1.338867969025159e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0414297878742218</v>
+        <v>2.79446776403347e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.01198846101760864</v>
+        <v>7.544938398496015e-06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.04846951737999916</v>
+        <v>2.952011755041895e-06</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.02276197634637356</v>
+        <v>1.722412707749754e-05</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.005350416526198387</v>
+        <v>9.219024832418654e-08</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.003663221141323447</v>
+        <v>2.719337089729379e-06</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.002468480262905359</v>
+        <v>6.810900686105015e-06</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.01405074261128902</v>
+        <v>4.709406857728027e-05</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.01531064324080944</v>
+        <v>8.854228326526936e-06</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.02368622832000256</v>
+        <v>4.195720248389989e-05</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.007965417578816414</v>
+        <v>1.118602449423634e-05</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.01135731302201748</v>
+        <v>1.17213630801416e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0255621038377285</v>
+        <v>1.786380926205311e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.002070903778076172</v>
+        <v>1.52578668348724e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.009353790432214737</v>
+        <v>2.921370287367608e-05</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.008280150592327118</v>
+        <v>1.099582004826516e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.003136767074465752</v>
+        <v>3.789646143559366e-07</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.01637963391840458</v>
+        <v>1.68783990375232e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.001592555548995733</v>
+        <v>1.726795744616538e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.04039239883422852</v>
+        <v>4.135527888138313e-06</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.009155898354947567</v>
+        <v>7.923954399302602e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.01395914331078529</v>
+        <v>1.04730247585394e-07</v>
       </c>
       <c r="EN3" t="n">
-        <v>4.635099321603775e-05</v>
+        <v>5.301410510583082e-06</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.01918167062103748</v>
+        <v>1.871698623290285e-05</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.002932690549641848</v>
+        <v>2.045917972282041e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.002230302430689335</v>
+        <v>2.310993295395747e-06</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.007514323107898235</v>
+        <v>2.966929059766699e-06</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03098803013563156</v>
+        <v>1.239915400219616e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01211322750896215</v>
+        <v>2.49910845013801e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.01184701733291149</v>
+        <v>9.07030698726885e-06</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.04350437223911285</v>
+        <v>4.554364295472624e-06</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.005258625838905573</v>
+        <v>1.626095217943657e-05</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.008193046785891056</v>
+        <v>1.951970625668764e-05</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0009385385783389211</v>
+        <v>1.61509833560558e-05</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.001606243080459535</v>
+        <v>1.229224199050805e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.01535456255078316</v>
+        <v>7.983244358911179e-06</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.01125826220959425</v>
+        <v>8.91456329554785e-06</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.005439217202365398</v>
+        <v>9.092147593037225e-06</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.004999054130166769</v>
+        <v>1.178848287963774e-05</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.01043805480003357</v>
+        <v>7.969077842062688e-07</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.0003346235025674105</v>
+        <v>1.274756755265116e-06</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.002481526229530573</v>
+        <v>3.999875843874179e-05</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.01462051644921303</v>
+        <v>1.145703299698653e-05</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.004974940791726112</v>
+        <v>9.956683243217412e-06</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.001226845197379589</v>
+        <v>3.575288246793207e-06</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.006333591882139444</v>
+        <v>1.701728797343094e-05</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.005561180878430605</v>
+        <v>2.525406489439774e-05</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.03656941652297974</v>
+        <v>5.081709787191357e-06</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.0190180167555809</v>
+        <v>4.019701691504451e-07</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.004362957552075386</v>
+        <v>4.015843842353206e-06</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.007827410474419594</v>
+        <v>1.611508378118742e-05</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.01821643114089966</v>
+        <v>3.512601097099832e-06</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.004467058461159468</v>
+        <v>4.146902938373387e-05</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.01802184246480465</v>
+        <v>7.350699161179364e-05</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.0623992346227169</v>
+        <v>1.438028357370058e-05</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.00935346819460392</v>
+        <v>4.450580490811262e-06</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.02421723864972591</v>
+        <v>4.411293957673479e-06</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.005284332670271397</v>
+        <v>2.332556960027432e-06</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.01374551467597485</v>
+        <v>5.628385224554222e-07</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.00454266183078289</v>
+        <v>3.649017889983952e-05</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.005346714053303003</v>
+        <v>8.823621442388685e-07</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.02389304898679256</v>
+        <v>1.97127496903704e-06</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.01485740672796965</v>
+        <v>8.091592462733388e-06</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.009174281731247902</v>
+        <v>5.623310426017269e-05</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.01531230378895998</v>
+        <v>5.727615643991157e-07</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.0138694616034627</v>
+        <v>1.23438267110032e-05</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.04497190192341805</v>
+        <v>5.295471783028916e-05</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.01555396057665348</v>
+        <v>7.623415058333194e-06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.95021374465432e-05</v>
+        <v>0.000232354155741632</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0005644230404868722</v>
+        <v>0.003913538530468941</v>
       </c>
       <c r="C4" t="n">
-        <v>3.492676478344947e-05</v>
+        <v>0.0003062231407966465</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003290019812993705</v>
+        <v>0.003315624548122287</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001854094734881073</v>
+        <v>0.001025918405503035</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001115302366088144</v>
+        <v>0.001042587100528181</v>
       </c>
       <c r="G4" t="n">
-        <v>5.460289685288444e-06</v>
+        <v>0.001060377922840416</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7491835023975e-05</v>
+        <v>0.0006888546631671488</v>
       </c>
       <c r="I4" t="n">
-        <v>7.607050065416843e-05</v>
+        <v>0.0002430634049233049</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001020668132696301</v>
+        <v>0.0004635229706764221</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0004318583814892918</v>
+        <v>0.004135267809033394</v>
       </c>
       <c r="L4" t="n">
-        <v>1.400992550770752e-05</v>
+        <v>0.0007186494185589254</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002544833696447313</v>
+        <v>0.004416404291987419</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000198332971194759</v>
+        <v>0.001598796807229519</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0001768567453837022</v>
+        <v>0.0004705708124674857</v>
       </c>
       <c r="P4" t="n">
-        <v>5.712304846383631e-05</v>
+        <v>0.001173011376522481</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001412971178069711</v>
+        <v>0.0001850839325925335</v>
       </c>
       <c r="R4" t="n">
-        <v>2.638590740389191e-05</v>
+        <v>9.836553363129497e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.184633401862811e-05</v>
+        <v>8.954992517828941e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>8.977026300271973e-05</v>
+        <v>7.136506610549986e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>2.270221011713147e-05</v>
+        <v>0.0001800884201657027</v>
       </c>
       <c r="V4" t="n">
-        <v>5.062887066742405e-05</v>
+        <v>8.738071483094245e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>4.689964407589287e-05</v>
+        <v>0.0002588566567283124</v>
       </c>
       <c r="X4" t="n">
-        <v>2.504169970052317e-05</v>
+        <v>0.0005311730783432722</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0001080749862012453</v>
+        <v>0.0004087853594683111</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.597612521843985e-05</v>
+        <v>0.0005978196277283132</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.310247459216043e-05</v>
+        <v>0.0006558708264492452</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.359679951448925e-05</v>
+        <v>6.784524885006249e-05</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.643237116397358e-05</v>
+        <v>0.0002330305724171922</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.81988819653634e-06</v>
+        <v>0.0001499942009104416</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.837205076706596e-05</v>
+        <v>0.000758275156840682</v>
       </c>
       <c r="AF4" t="n">
-        <v>5.187002898310311e-05</v>
+        <v>0.000194066102267243</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.071751441690139e-05</v>
+        <v>0.0004792715772055089</v>
       </c>
       <c r="AH4" t="n">
-        <v>7.096472472767346e-06</v>
+        <v>0.0003576260060071945</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.613159788073972e-05</v>
+        <v>0.0001694221718935296</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5.797026460641064e-05</v>
+        <v>6.391646456904709e-05</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.210851693642326e-05</v>
+        <v>4.898314728052355e-05</v>
       </c>
       <c r="AL4" t="n">
-        <v>6.749592284904793e-05</v>
+        <v>0.001090642414055765</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.20046879601432e-05</v>
+        <v>0.0002986483450513333</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.202028892701492e-05</v>
+        <v>0.0006213990272954106</v>
       </c>
       <c r="AO4" t="n">
-        <v>3.775609229705879e-06</v>
+        <v>0.0004550453159026802</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.483869896735996e-05</v>
+        <v>0.0006874167593196034</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.188838309142739e-05</v>
+        <v>0.0002310045820195228</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.148489657993196e-06</v>
+        <v>0.0003172159777022898</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.244579758960754e-05</v>
+        <v>9.351628978038207e-05</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.910567314364016e-05</v>
+        <v>0.0001391587138641626</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0003493562981020659</v>
+        <v>0.002424115780740976</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.063616400642786e-05</v>
+        <v>0.0002473343629390001</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.0001448950206395239</v>
+        <v>0.001501902705058455</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.402789636515081e-05</v>
+        <v>0.002062689047306776</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.059844726114534e-05</v>
+        <v>0.000367219268810004</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.266181349521503e-05</v>
+        <v>6.175628368509933e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.498516550986096e-05</v>
+        <v>0.0003958551678806543</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.971018931129947e-05</v>
+        <v>0.0002084620937239379</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.426550706033595e-05</v>
+        <v>0.0003719657543115318</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.996991917025298e-05</v>
+        <v>4.666518361773342e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.32036166684702e-05</v>
+        <v>0.0006112607661634684</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.081605973420665e-05</v>
+        <v>3.476884739939123e-05</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0001996781211346388</v>
+        <v>0.0007826567161828279</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.703992453869432e-05</v>
+        <v>0.0005437290528789163</v>
       </c>
       <c r="BI4" t="n">
-        <v>6.383062282111496e-05</v>
+        <v>0.0001824752107495442</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0001226569875143468</v>
+        <v>0.0008699928293935955</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.608943784958683e-05</v>
+        <v>0.0005173214012756944</v>
       </c>
       <c r="BL4" t="n">
-        <v>6.29506102995947e-05</v>
+        <v>0.0001187361631309614</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.428252446406987e-05</v>
+        <v>0.0004010068660136312</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.593066892586648e-05</v>
+        <v>0.0001550151209812611</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.944041863083839e-05</v>
+        <v>0.0004599476233124733</v>
       </c>
       <c r="BP4" t="n">
-        <v>9.402923751622438e-06</v>
+        <v>0.0005795634933747351</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.309436240466312e-06</v>
+        <v>0.0001966704585356638</v>
       </c>
       <c r="BR4" t="n">
-        <v>2.824966941261664e-06</v>
+        <v>2.514291190891527e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.64255086221965e-05</v>
+        <v>0.0001572235196363181</v>
       </c>
       <c r="BT4" t="n">
-        <v>2.535343082854524e-05</v>
+        <v>6.910196680109948e-05</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.774959234055132e-05</v>
+        <v>5.477092145156348e-06</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0001860674237832427</v>
+        <v>0.001428025308996439</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.285157269303454e-06</v>
+        <v>6.985299842199311e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>4.819018431589939e-05</v>
+        <v>0.001002646167762578</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.422653440386057e-06</v>
+        <v>0.0003951867111027241</v>
       </c>
       <c r="BZ4" t="n">
-        <v>8.054111822275445e-05</v>
+        <v>0.0004964555846527219</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.785793524002656e-05</v>
+        <v>0.0006213353481143713</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.806946940836497e-05</v>
+        <v>0.0001690179778961465</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.441789496922866e-05</v>
+        <v>0.0004262363654561341</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.8225844289409e-05</v>
+        <v>5.145738032297231e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0001014398148981854</v>
+        <v>0.001217261189594865</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.702575486386195e-05</v>
+        <v>0.000133793699205853</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.215341373812407e-05</v>
+        <v>0.001007502200081944</v>
       </c>
       <c r="CH4" t="n">
-        <v>5.77084665565053e-06</v>
+        <v>0.000163723569130525</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.475152177794371e-05</v>
+        <v>5.903062265133485e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.489278995199129e-05</v>
+        <v>2.179704097216018e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>6.566854608536232e-06</v>
+        <v>1.813986818888225e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>4.60420960735064e-05</v>
+        <v>0.0001703211455605924</v>
       </c>
       <c r="CM4" t="n">
-        <v>5.049696483183652e-05</v>
+        <v>6.631999713135883e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>7.158321750466712e-06</v>
+        <v>0.001189038157463074</v>
       </c>
       <c r="CO4" t="n">
-        <v>6.239477079361677e-05</v>
+        <v>0.0006717984797433019</v>
       </c>
       <c r="CP4" t="n">
-        <v>6.829000631114468e-05</v>
+        <v>0.001014345441944897</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0001096142368623987</v>
+        <v>0.000108960251964163</v>
       </c>
       <c r="CR4" t="n">
-        <v>4.316132981330156e-05</v>
+        <v>0.0001771375245880336</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.486719288048334e-05</v>
+        <v>0.0003283388214185834</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0001572473411215469</v>
+        <v>0.0005216641002334654</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.172958764072973e-05</v>
+        <v>0.0002882722183130682</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.587751441751607e-05</v>
+        <v>9.563432104187086e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>8.313258149428293e-05</v>
+        <v>0.001288074068725109</v>
       </c>
       <c r="CX4" t="n">
-        <v>3.092512270086445e-05</v>
+        <v>0.0001460153143852949</v>
       </c>
       <c r="CY4" t="n">
-        <v>6.969712558202446e-05</v>
+        <v>0.001099164597690105</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.147498318867292e-06</v>
+        <v>0.000296086393063888</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.94023884634953e-05</v>
+        <v>0.0001164854475064203</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.746110137901269e-05</v>
+        <v>7.74184718466131e-06</v>
       </c>
       <c r="DC4" t="n">
-        <v>7.960807124618441e-08</v>
+        <v>8.779152267379686e-06</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.299912350485101e-05</v>
+        <v>0.0002289998519700021</v>
       </c>
       <c r="DE4" t="n">
-        <v>3.932394611183554e-05</v>
+        <v>0.0006765081780031323</v>
       </c>
       <c r="DF4" t="n">
-        <v>9.776052320376039e-05</v>
+        <v>0.0008688404923304915</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.512847251840867e-05</v>
+        <v>0.0003701512468978763</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0001385756768286228</v>
+        <v>0.0008708077948540449</v>
       </c>
       <c r="DI4" t="n">
-        <v>3.112448393949308e-05</v>
+        <v>0.0006865148316137493</v>
       </c>
       <c r="DJ4" t="n">
-        <v>4.080711732967757e-06</v>
+        <v>0.0009986201766878366</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.945458153495565e-05</v>
+        <v>0.0005371219012886286</v>
       </c>
       <c r="DL4" t="n">
-        <v>9.438893903279677e-05</v>
+        <v>0.0009930479573085904</v>
       </c>
       <c r="DM4" t="n">
-        <v>2.588431198091712e-05</v>
+        <v>4.591588731273077e-05</v>
       </c>
       <c r="DN4" t="n">
-        <v>9.29955713218078e-05</v>
+        <v>0.0001873408327810466</v>
       </c>
       <c r="DO4" t="n">
-        <v>6.162605131976306e-05</v>
+        <v>0.0007033211877569556</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.863798939273693e-07</v>
+        <v>6.760289397789165e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.58980456541758e-06</v>
+        <v>0.0007919945055618882</v>
       </c>
       <c r="DR4" t="n">
-        <v>2.208797377534211e-05</v>
+        <v>0.000388981425203383</v>
       </c>
       <c r="DS4" t="n">
-        <v>7.842845661798492e-05</v>
+        <v>0.000314446137053892</v>
       </c>
       <c r="DT4" t="n">
-        <v>8.003203220141586e-06</v>
+        <v>0.0008650236995890737</v>
       </c>
       <c r="DU4" t="n">
-        <v>9.050480912264902e-06</v>
+        <v>0.0004471971769817173</v>
       </c>
       <c r="DV4" t="n">
-        <v>4.68136349809356e-05</v>
+        <v>0.001123227877542377</v>
       </c>
       <c r="DW4" t="n">
-        <v>3.521428880048916e-05</v>
+        <v>9.869554196484387e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>3.159154948662035e-05</v>
+        <v>0.0004315224068704993</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0001255433890037239</v>
+        <v>2.488736208761111e-05</v>
       </c>
       <c r="DZ4" t="n">
-        <v>2.005881469813175e-05</v>
+        <v>0.0006390086491592228</v>
       </c>
       <c r="EA4" t="n">
-        <v>6.61625963402912e-05</v>
+        <v>0.0003889404470100999</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.77702368091559e-05</v>
+        <v>0.000911081035155803</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.46480976784369e-06</v>
+        <v>0.0001043060619849712</v>
       </c>
       <c r="ED4" t="n">
-        <v>4.652453935705125e-05</v>
+        <v>0.00183409615419805</v>
       </c>
       <c r="EE4" t="n">
-        <v>1.540031189506408e-05</v>
+        <v>0.0007563830004073679</v>
       </c>
       <c r="EF4" t="n">
-        <v>3.155260128551163e-05</v>
+        <v>0.0003214154858142138</v>
       </c>
       <c r="EG4" t="n">
-        <v>4.676160097005777e-05</v>
+        <v>0.000732062675524503</v>
       </c>
       <c r="EH4" t="n">
-        <v>2.388520215390599e-06</v>
+        <v>0.0002455190697219223</v>
       </c>
       <c r="EI4" t="n">
-        <v>2.373777169850655e-05</v>
+        <v>0.0008912443881854415</v>
       </c>
       <c r="EJ4" t="n">
-        <v>4.401837213663384e-05</v>
+        <v>0.0004055087047163397</v>
       </c>
       <c r="EK4" t="n">
-        <v>2.551108627812937e-05</v>
+        <v>3.668796853162348e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>3.038130489585456e-05</v>
+        <v>0.0001276266266359016</v>
       </c>
       <c r="EM4" t="n">
-        <v>3.878053030348383e-05</v>
+        <v>3.439944703131914e-05</v>
       </c>
       <c r="EN4" t="n">
-        <v>7.956773515616078e-06</v>
+        <v>7.881569035816938e-05</v>
       </c>
       <c r="EO4" t="n">
-        <v>4.546209311229177e-05</v>
+        <v>6.83249527355656e-05</v>
       </c>
       <c r="EP4" t="n">
-        <v>5.49376527487766e-05</v>
+        <v>0.001077825203537941</v>
       </c>
       <c r="EQ4" t="n">
-        <v>8.605196853750385e-06</v>
+        <v>3.107330485363491e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>7.135181658668444e-05</v>
+        <v>0.0003175652236677706</v>
       </c>
       <c r="ES4" t="n">
-        <v>3.097944136243314e-05</v>
+        <v>0.0002379439538344741</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0001646932505536824</v>
+        <v>0.0004539532237686217</v>
       </c>
       <c r="EU4" t="n">
-        <v>2.225334810646018e-06</v>
+        <v>0.0003730099415406585</v>
       </c>
       <c r="EV4" t="n">
-        <v>1.605903344170656e-05</v>
+        <v>0.0001491069851908833</v>
       </c>
       <c r="EW4" t="n">
-        <v>1.236806929227896e-05</v>
+        <v>0.0006100384634919465</v>
       </c>
       <c r="EX4" t="n">
-        <v>2.197082176280674e-05</v>
+        <v>7.073707820381969e-06</v>
       </c>
       <c r="EY4" t="n">
-        <v>8.097590762190521e-05</v>
+        <v>0.001306696678511798</v>
       </c>
       <c r="EZ4" t="n">
-        <v>1.98584621102782e-05</v>
+        <v>5.781788058811799e-05</v>
       </c>
       <c r="FA4" t="n">
-        <v>4.759800140163861e-05</v>
+        <v>0.001095446990802884</v>
       </c>
       <c r="FB4" t="n">
-        <v>3.377313987584785e-06</v>
+        <v>0.0002056023949990049</v>
       </c>
       <c r="FC4" t="n">
-        <v>2.535561179684009e-05</v>
+        <v>0.0001157870792667381</v>
       </c>
       <c r="FD4" t="n">
-        <v>2.613383549032733e-05</v>
+        <v>7.597014337079599e-05</v>
       </c>
       <c r="FE4" t="n">
-        <v>3.49733090843074e-06</v>
+        <v>0.0001862653734860942</v>
       </c>
       <c r="FF4" t="n">
-        <v>3.961419133702293e-05</v>
+        <v>0.0002642192994244397</v>
       </c>
       <c r="FG4" t="n">
-        <v>7.817288860678673e-06</v>
+        <v>8.288134995382279e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>4.374131094664335e-05</v>
+        <v>0.0004096311749890447</v>
       </c>
       <c r="FI4" t="n">
-        <v>4.250609345035627e-05</v>
+        <v>0.0004995318595319986</v>
       </c>
       <c r="FJ4" t="n">
-        <v>8.474839705741033e-05</v>
+        <v>0.000270162767264992</v>
       </c>
       <c r="FK4" t="n">
-        <v>1.001506461761892e-05</v>
+        <v>0.0001394103455822915</v>
       </c>
       <c r="FL4" t="n">
-        <v>1.108201786337304e-06</v>
+        <v>0.0003722775145433843</v>
       </c>
       <c r="FM4" t="n">
-        <v>4.01408615289256e-05</v>
+        <v>0.0002609735238365829</v>
       </c>
       <c r="FN4" t="n">
-        <v>2.091888927679975e-05</v>
+        <v>0.0008731286507099867</v>
       </c>
       <c r="FO4" t="n">
-        <v>8.965341839939356e-05</v>
+        <v>0.0006119083263911307</v>
       </c>
       <c r="FP4" t="n">
-        <v>6.459559517679736e-05</v>
+        <v>0.0003484167682472616</v>
       </c>
       <c r="FQ4" t="n">
-        <v>4.127227657590993e-05</v>
+        <v>0.0003987246309407055</v>
       </c>
       <c r="FR4" t="n">
-        <v>6.029556971043348e-05</v>
+        <v>0.0001167383597930893</v>
       </c>
       <c r="FS4" t="n">
-        <v>9.866706386674196e-05</v>
+        <v>0.001115689286962152</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0001951812300831079</v>
+        <v>0.0004655795637518167</v>
       </c>
       <c r="FU4" t="n">
-        <v>1.295507900067605e-05</v>
+        <v>0.0008329296833835542</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.574399150034878e-05</v>
+        <v>8.032061305129901e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>6.191017746459693e-05</v>
+        <v>7.515313336625695e-05</v>
       </c>
       <c r="FX4" t="n">
-        <v>5.83019937039353e-05</v>
+        <v>0.001163664273917675</v>
       </c>
       <c r="FY4" t="n">
-        <v>5.460530519485474e-05</v>
+        <v>0.0003081419854424894</v>
       </c>
       <c r="FZ4" t="n">
-        <v>2.458851849951316e-05</v>
+        <v>0.0006586639792658389</v>
       </c>
       <c r="GA4" t="n">
-        <v>5.419295484898612e-05</v>
+        <v>0.0002337514160899445</v>
       </c>
       <c r="GB4" t="n">
-        <v>2.382491584285162e-05</v>
+        <v>0.0009302055113948882</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0001100122535717674</v>
+        <v>0.001229276182129979</v>
       </c>
       <c r="GD4" t="n">
-        <v>4.450673441169783e-05</v>
+        <v>0.0003356434172019362</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.000126091341371648</v>
+        <v>0.001091670477762818</v>
       </c>
       <c r="GF4" t="n">
-        <v>8.008089935174212e-06</v>
+        <v>0.0003134542494080961</v>
       </c>
       <c r="GG4" t="n">
-        <v>4.026104215881787e-05</v>
+        <v>0.0001375973515678197</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3.64714423994883e-07</v>
+        <v>0.001038472866639495</v>
       </c>
       <c r="B5" t="n">
-        <v>4.214244108879939e-05</v>
+        <v>0.001902043004520237</v>
       </c>
       <c r="C5" t="n">
-        <v>6.933858912816504e-06</v>
+        <v>0.0002460531832184643</v>
       </c>
       <c r="D5" t="n">
-        <v>1.611472907825373e-05</v>
+        <v>0.00037309032632038</v>
       </c>
       <c r="E5" t="n">
-        <v>1.894635897770058e-05</v>
+        <v>0.000199615431483835</v>
       </c>
       <c r="F5" t="n">
-        <v>2.58806103374809e-05</v>
+        <v>0.002011066302657127</v>
       </c>
       <c r="G5" t="n">
-        <v>8.503575372742489e-07</v>
+        <v>0.0006708480650559068</v>
       </c>
       <c r="H5" t="n">
-        <v>6.79095819577924e-06</v>
+        <v>0.0007774019613862038</v>
       </c>
       <c r="I5" t="n">
-        <v>3.189028120686999e-06</v>
+        <v>0.0004511807928793132</v>
       </c>
       <c r="J5" t="n">
-        <v>1.364248419122305e-06</v>
+        <v>0.0009292261675000191</v>
       </c>
       <c r="K5" t="n">
-        <v>3.867799387080595e-05</v>
+        <v>0.002398184966295958</v>
       </c>
       <c r="L5" t="n">
-        <v>4.468158749659779e-06</v>
+        <v>0.0003693019971251488</v>
       </c>
       <c r="M5" t="n">
-        <v>2.020253123191651e-05</v>
+        <v>3.517981531331316e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>2.585345282568596e-05</v>
+        <v>0.0005497958045452833</v>
       </c>
       <c r="O5" t="n">
-        <v>2.951855458377395e-05</v>
+        <v>0.001970496261492372</v>
       </c>
       <c r="P5" t="n">
-        <v>1.106608578993473e-05</v>
+        <v>0.0002355852775508538</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.953962267492898e-06</v>
+        <v>2.428234438411891e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>4.393998096929863e-06</v>
+        <v>0.0009340380202047527</v>
       </c>
       <c r="S5" t="n">
-        <v>1.793987394194119e-06</v>
+        <v>8.131152571877465e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>8.593217899033334e-06</v>
+        <v>0.0003209462738595903</v>
       </c>
       <c r="U5" t="n">
-        <v>2.849376642188872e-06</v>
+        <v>0.000428273226134479</v>
       </c>
       <c r="V5" t="n">
-        <v>1.243416932084074e-06</v>
+        <v>0.0005260868929326534</v>
       </c>
       <c r="W5" t="n">
-        <v>2.487719029886648e-06</v>
+        <v>0.0002277922758366913</v>
       </c>
       <c r="X5" t="n">
-        <v>7.469224328815471e-06</v>
+        <v>0.0001208882822538726</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.986793788295472e-06</v>
+        <v>0.0001422307395841926</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.893161869607866e-08</v>
+        <v>0.0006121225887909532</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.104765700205462e-07</v>
+        <v>0.0001934741594595835</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.177843831916107e-06</v>
+        <v>8.144437742885202e-05</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.170156666485127e-06</v>
+        <v>0.0004558225045911968</v>
       </c>
       <c r="AD5" t="n">
-        <v>9.568155292072333e-06</v>
+        <v>3.032927997992374e-05</v>
       </c>
       <c r="AE5" t="n">
-        <v>7.412808372464497e-06</v>
+        <v>0.0007969308644533157</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.095018797059311e-05</v>
+        <v>0.0006639540079049766</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.171516138740117e-06</v>
+        <v>0.000220117173739709</v>
       </c>
       <c r="AH5" t="n">
-        <v>7.176870894909371e-06</v>
+        <v>3.521492180880159e-05</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.428183840194833e-07</v>
+        <v>0.001059199334122241</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.567879053254728e-06</v>
+        <v>0.0001311790838371962</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.296710019640159e-06</v>
+        <v>0.0001185921719297767</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.24132508164621e-06</v>
+        <v>0.0003536817966960371</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.89561660590698e-06</v>
+        <v>0.0004626074805855751</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.92416939373652e-06</v>
+        <v>0.0004544113180600107</v>
       </c>
       <c r="AO5" t="n">
-        <v>3.15773399961472e-06</v>
+        <v>0.0001751780073391274</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.21942820341792e-06</v>
+        <v>0.0002996658440679312</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.524357114452869e-06</v>
+        <v>0.0001599487732164562</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.160885858553229e-07</v>
+        <v>0.0006082007894292474</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.213756715718773e-06</v>
+        <v>0.0003155536251142621</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.738050731451949e-06</v>
+        <v>0.0004489081911742687</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.060988819925115e-05</v>
+        <v>0.001820834469981492</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.309290251418133e-07</v>
+        <v>0.0003367029712535441</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.964589046110632e-06</v>
+        <v>7.47748272260651e-05</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.382355528941844e-06</v>
+        <v>0.0002966097381431609</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.633290806552395e-06</v>
+        <v>0.001138978870585561</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.036504727380816e-05</v>
+        <v>4.702060687122867e-05</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.755786110559711e-06</v>
+        <v>0.0001101634261431172</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.478871571540367e-06</v>
+        <v>0.0002672999107744545</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.805050922295777e-07</v>
+        <v>6.665712135145441e-06</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.168958806374576e-05</v>
+        <v>0.0001353348634438589</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.442259175149957e-06</v>
+        <v>0.0003167552931699902</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.339841663953848e-06</v>
+        <v>5.662301555275917e-05</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.705784936551936e-05</v>
+        <v>0.0001641667186049744</v>
       </c>
       <c r="BH5" t="n">
-        <v>1.707946466922294e-05</v>
+        <v>0.0005240899045020342</v>
       </c>
       <c r="BI5" t="n">
-        <v>8.821770279610064e-06</v>
+        <v>7.799365266691893e-05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4.97473229188472e-06</v>
+        <v>0.0007204855792224407</v>
       </c>
       <c r="BK5" t="n">
-        <v>2.326927642570809e-06</v>
+        <v>0.0003687589196488261</v>
       </c>
       <c r="BL5" t="n">
-        <v>7.387156529148342e-06</v>
+        <v>3.624337841756642e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.743399020095239e-06</v>
+        <v>0.0004297936975490302</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.663872914534295e-06</v>
+        <v>2.942975152109284e-05</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.072834999784391e-07</v>
+        <v>0.0001417050079908222</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.447416252631228e-06</v>
+        <v>0.0004596659855451435</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.9414110283833e-06</v>
+        <v>0.0004412787966430187</v>
       </c>
       <c r="BR5" t="n">
-        <v>4.901234206045046e-06</v>
+        <v>0.0007701573777012527</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.787502469596802e-06</v>
+        <v>4.756953421747312e-05</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.985655671887798e-06</v>
+        <v>0.0005775297177024186</v>
       </c>
       <c r="BU5" t="n">
-        <v>2.87034936263808e-06</v>
+        <v>9.72503621596843e-05</v>
       </c>
       <c r="BV5" t="n">
-        <v>1.602287375135347e-05</v>
+        <v>0.001284738071262836</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.18134902449674e-06</v>
+        <v>0.0002830234589055181</v>
       </c>
       <c r="BX5" t="n">
-        <v>3.156890670652501e-06</v>
+        <v>0.0004950670409016311</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.63530228039599e-06</v>
+        <v>0.000102560399682261</v>
       </c>
       <c r="BZ5" t="n">
-        <v>6.003530415910063e-06</v>
+        <v>0.0007312538800761104</v>
       </c>
       <c r="CA5" t="n">
-        <v>5.447305738925934e-06</v>
+        <v>0.0002519713598303497</v>
       </c>
       <c r="CB5" t="n">
-        <v>2.049982867902145e-06</v>
+        <v>1.00072065833956e-05</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.689573813720926e-07</v>
+        <v>0.0002710844564717263</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.725014383031521e-07</v>
+        <v>0.000464733486296609</v>
       </c>
       <c r="CE5" t="n">
-        <v>7.63746902521234e-06</v>
+        <v>0.0005821982631459832</v>
       </c>
       <c r="CF5" t="n">
-        <v>4.205566597192956e-07</v>
+        <v>0.000105233360955026</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.420018972770777e-06</v>
+        <v>0.0003405878087505698</v>
       </c>
       <c r="CH5" t="n">
-        <v>4.766291397118039e-07</v>
+        <v>0.0002743151562754065</v>
       </c>
       <c r="CI5" t="n">
-        <v>3.039528337467345e-06</v>
+        <v>0.0005253006238490343</v>
       </c>
       <c r="CJ5" t="n">
-        <v>5.482724191097077e-06</v>
+        <v>0.0002905704022850841</v>
       </c>
       <c r="CK5" t="n">
-        <v>3.377832058504282e-07</v>
+        <v>0.0001244440209120512</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.329261522187153e-06</v>
+        <v>9.930280066328123e-05</v>
       </c>
       <c r="CM5" t="n">
-        <v>5.563303147937404e-06</v>
+        <v>0.0001156775397248566</v>
       </c>
       <c r="CN5" t="n">
-        <v>7.963386451592669e-06</v>
+        <v>0.001096887164749205</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.537576281407382e-06</v>
+        <v>0.000252180325333029</v>
       </c>
       <c r="CP5" t="n">
-        <v>3.711694716912461e-06</v>
+        <v>8.588787750340998e-05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>5.844080533279339e-06</v>
+        <v>0.000236602863878943</v>
       </c>
       <c r="CR5" t="n">
-        <v>3.509113412292209e-06</v>
+        <v>0.0002531196805648506</v>
       </c>
       <c r="CS5" t="n">
-        <v>7.507619557145517e-06</v>
+        <v>0.000651706475764513</v>
       </c>
       <c r="CT5" t="n">
-        <v>1.564910417073406e-05</v>
+        <v>0.0002724292280618101</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.282324546991731e-06</v>
+        <v>0.0001843653881223872</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.099156972690253e-07</v>
+        <v>0.0003640528593678027</v>
       </c>
       <c r="CW5" t="n">
-        <v>5.452372988656862e-06</v>
+        <v>0.0005084070726297796</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.82391318048758e-06</v>
+        <v>7.947694393806159e-05</v>
       </c>
       <c r="CY5" t="n">
-        <v>3.000613560288912e-06</v>
+        <v>0.0003109662502538413</v>
       </c>
       <c r="CZ5" t="n">
-        <v>7.462675739589031e-07</v>
+        <v>0.0002300907362950966</v>
       </c>
       <c r="DA5" t="n">
-        <v>4.005466962553328e-06</v>
+        <v>0.0004865968076046556</v>
       </c>
       <c r="DB5" t="n">
-        <v>3.670764499474899e-06</v>
+        <v>0.0001681462454143912</v>
       </c>
       <c r="DC5" t="n">
-        <v>4.903437798020605e-07</v>
+        <v>0.0001538740762043744</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.487768486185814e-06</v>
+        <v>9.13746771402657e-05</v>
       </c>
       <c r="DE5" t="n">
-        <v>6.061878593754955e-06</v>
+        <v>8.157576667144895e-05</v>
       </c>
       <c r="DF5" t="n">
-        <v>8.369548595510423e-06</v>
+        <v>0.0005701772752217948</v>
       </c>
       <c r="DG5" t="n">
-        <v>8.531176717951894e-06</v>
+        <v>0.0002294569276273251</v>
       </c>
       <c r="DH5" t="n">
-        <v>4.672644536185544e-06</v>
+        <v>0.0001989112934097648</v>
       </c>
       <c r="DI5" t="n">
-        <v>4.81299139210023e-06</v>
+        <v>0.0006378333200700581</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.247072123078397e-05</v>
+        <v>0.0002044304274022579</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.081967174191959e-06</v>
+        <v>6.701573147438467e-05</v>
       </c>
       <c r="DL5" t="n">
-        <v>1.812691152736079e-07</v>
+        <v>0.0004426416126079857</v>
       </c>
       <c r="DM5" t="n">
-        <v>2.218930148956133e-06</v>
+        <v>0.0002948033506982028</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.49080449318717e-07</v>
+        <v>3.968678356613964e-05</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.802458422796917e-06</v>
+        <v>0.0003230447764508426</v>
       </c>
       <c r="DP5" t="n">
-        <v>2.848607891792199e-06</v>
+        <v>0.0002195658453274518</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1.048607919074129e-05</v>
+        <v>0.0003848359920084476</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.404259693226777e-06</v>
+        <v>0.000255608931183815</v>
       </c>
       <c r="DS5" t="n">
-        <v>6.778177066735225e-06</v>
+        <v>0.0004621402476914227</v>
       </c>
       <c r="DT5" t="n">
-        <v>2.526797743485076e-06</v>
+        <v>0.000150227831909433</v>
       </c>
       <c r="DU5" t="n">
-        <v>2.309310957571142e-06</v>
+        <v>0.0003659969079308212</v>
       </c>
       <c r="DV5" t="n">
-        <v>1.248462126568484e-06</v>
+        <v>0.0001791703689377755</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.935338104885886e-06</v>
+        <v>0.0001991649478441104</v>
       </c>
       <c r="DX5" t="n">
-        <v>2.572582161519676e-06</v>
+        <v>3.382320574019104e-05</v>
       </c>
       <c r="DY5" t="n">
-        <v>1.902211010929022e-07</v>
+        <v>4.670728230848908e-05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>9.869573659671005e-06</v>
+        <v>4.872766294283792e-05</v>
       </c>
       <c r="EA5" t="n">
-        <v>2.205917553510517e-06</v>
+        <v>0.0004048930131830275</v>
       </c>
       <c r="EB5" t="n">
-        <v>6.173380825202912e-06</v>
+        <v>0.0006242436938919127</v>
       </c>
       <c r="EC5" t="n">
-        <v>6.681274498987477e-06</v>
+        <v>0.0002048383321380243</v>
       </c>
       <c r="ED5" t="n">
-        <v>9.563896128383931e-06</v>
+        <v>0.0002209586091339588</v>
       </c>
       <c r="EE5" t="n">
-        <v>3.181460897394572e-06</v>
+        <v>0.0006351183983497322</v>
       </c>
       <c r="EF5" t="n">
-        <v>1.847175326474826e-06</v>
+        <v>0.000488855701405555</v>
       </c>
       <c r="EG5" t="n">
-        <v>5.433284513856051e-06</v>
+        <v>4.289205025997944e-05</v>
       </c>
       <c r="EH5" t="n">
-        <v>1.287077338929521e-06</v>
+        <v>0.0002349257993046194</v>
       </c>
       <c r="EI5" t="n">
-        <v>5.862798388989177e-06</v>
+        <v>0.0003680979716591537</v>
       </c>
       <c r="EJ5" t="n">
-        <v>1.181031393571175e-06</v>
+        <v>0.0003747363807633519</v>
       </c>
       <c r="EK5" t="n">
-        <v>9.094928827835247e-07</v>
+        <v>0.000169709644978866</v>
       </c>
       <c r="EL5" t="n">
-        <v>9.156424312095623e-06</v>
+        <v>9.344569843960926e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>6.287493761192309e-07</v>
+        <v>2.942636456282344e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>3.979110942964326e-07</v>
+        <v>0.0001644090953050181</v>
       </c>
       <c r="EO5" t="n">
-        <v>1.637351942918031e-06</v>
+        <v>0.0002855276688933372</v>
       </c>
       <c r="EP5" t="n">
-        <v>2.535610519771581e-06</v>
+        <v>0.0003125516232103109</v>
       </c>
       <c r="EQ5" t="n">
-        <v>3.993925474787829e-06</v>
+        <v>0.0001413455902365968</v>
       </c>
       <c r="ER5" t="n">
-        <v>4.311905286158435e-06</v>
+        <v>0.0005204244516789913</v>
       </c>
       <c r="ES5" t="n">
-        <v>5.871602297702339e-06</v>
+        <v>0.0006626038230024278</v>
       </c>
       <c r="ET5" t="n">
-        <v>1.217666249431204e-05</v>
+        <v>0.0004235543310642242</v>
       </c>
       <c r="EU5" t="n">
-        <v>8.823841426419676e-07</v>
+        <v>5.762775253970176e-05</v>
       </c>
       <c r="EV5" t="n">
-        <v>3.690521452881512e-06</v>
+        <v>0.000175117515027523</v>
       </c>
       <c r="EW5" t="n">
-        <v>2.144810196114122e-06</v>
+        <v>0.0003762681153602898</v>
       </c>
       <c r="EX5" t="n">
-        <v>8.944076625994057e-07</v>
+        <v>0.0004378829034976661</v>
       </c>
       <c r="EY5" t="n">
-        <v>5.933100965194171e-06</v>
+        <v>0.0006373944343067706</v>
       </c>
       <c r="EZ5" t="n">
-        <v>3.165530415571993e-08</v>
+        <v>4.826040822081268e-05</v>
       </c>
       <c r="FA5" t="n">
-        <v>2.719115400395822e-06</v>
+        <v>0.0002714193251449615</v>
       </c>
       <c r="FB5" t="n">
-        <v>1.357632072540582e-06</v>
+        <v>0.0003430911165196449</v>
       </c>
       <c r="FC5" t="n">
-        <v>4.502900537772803e-06</v>
+        <v>0.000415550428442657</v>
       </c>
       <c r="FD5" t="n">
-        <v>4.108602297492325e-06</v>
+        <v>0.0002495019289199263</v>
       </c>
       <c r="FE5" t="n">
-        <v>1.572169480823504e-06</v>
+        <v>0.0001372651458950713</v>
       </c>
       <c r="FF5" t="n">
-        <v>1.313673124059278e-06</v>
+        <v>8.035722567001358e-05</v>
       </c>
       <c r="FG5" t="n">
-        <v>3.155114427499939e-07</v>
+        <v>0.00026524523855187</v>
       </c>
       <c r="FH5" t="n">
-        <v>5.430260330285819e-07</v>
+        <v>0.0007003135979175568</v>
       </c>
       <c r="FI5" t="n">
-        <v>1.743482698657317e-06</v>
+        <v>0.0002089956396957859</v>
       </c>
       <c r="FJ5" t="n">
-        <v>1.343931853625691e-05</v>
+        <v>0.0003861237491946667</v>
       </c>
       <c r="FK5" t="n">
-        <v>9.677722118794918e-06</v>
+        <v>0.0001565856800880283</v>
       </c>
       <c r="FL5" t="n">
-        <v>5.077818059362471e-06</v>
+        <v>0.0007454394362866879</v>
       </c>
       <c r="FM5" t="n">
-        <v>4.946501576341689e-06</v>
+        <v>0.0003943938063457608</v>
       </c>
       <c r="FN5" t="n">
-        <v>1.099860855902079e-05</v>
+        <v>0.0009138220921158791</v>
       </c>
       <c r="FO5" t="n">
-        <v>5.455078280647285e-06</v>
+        <v>0.0002665176871232688</v>
       </c>
       <c r="FP5" t="n">
-        <v>3.374105745024281e-06</v>
+        <v>0.0002088039327645674</v>
       </c>
       <c r="FQ5" t="n">
-        <v>1.108205833588727e-05</v>
+        <v>0.0004121694655623287</v>
       </c>
       <c r="FR5" t="n">
-        <v>4.482879376155324e-06</v>
+        <v>0.0007390720420517027</v>
       </c>
       <c r="FS5" t="n">
-        <v>1.432934368494898e-05</v>
+        <v>0.0001996252685785294</v>
       </c>
       <c r="FT5" t="n">
-        <v>8.953546057455242e-06</v>
+        <v>9.721639798954129e-05</v>
       </c>
       <c r="FU5" t="n">
-        <v>9.78572825260926e-06</v>
+        <v>0.0001812459086067975</v>
       </c>
       <c r="FV5" t="n">
-        <v>6.062823558750097e-06</v>
+        <v>0.0002576336264610291</v>
       </c>
       <c r="FW5" t="n">
-        <v>2.631009465403622e-06</v>
+        <v>0.000502362207043916</v>
       </c>
       <c r="FX5" t="n">
-        <v>4.466858626983594e-06</v>
+        <v>0.0005566343897953629</v>
       </c>
       <c r="FY5" t="n">
-        <v>2.426259015919641e-08</v>
+        <v>0.0004825176438316703</v>
       </c>
       <c r="FZ5" t="n">
-        <v>5.641939424094744e-06</v>
+        <v>0.0001761064631864429</v>
       </c>
       <c r="GA5" t="n">
-        <v>9.668593520473223e-06</v>
+        <v>0.000259106804151088</v>
       </c>
       <c r="GB5" t="n">
-        <v>6.747013685526326e-07</v>
+        <v>0.0005021053366363049</v>
       </c>
       <c r="GC5" t="n">
-        <v>4.686476131610107e-06</v>
+        <v>0.0006159176700748503</v>
       </c>
       <c r="GD5" t="n">
-        <v>1.582426307322748e-06</v>
+        <v>0.0004693983937613666</v>
       </c>
       <c r="GE5" t="n">
-        <v>2.359959125897149e-06</v>
+        <v>5.310641427058727e-05</v>
       </c>
       <c r="GF5" t="n">
-        <v>4.348205038695596e-06</v>
+        <v>0.0001175388606498018</v>
       </c>
       <c r="GG5" t="n">
-        <v>3.572118203010177e-06</v>
+        <v>0.0005810951115563512</v>
       </c>
     </row>
     <row r="6">
@@ -3844,571 +3844,571 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.01161121018230915</v>
+        <v>0.0006285635754466057</v>
       </c>
       <c r="B7" t="n">
-        <v>0.04996137693524361</v>
+        <v>0.009763564914464951</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004602121654897928</v>
+        <v>0.001041475217789412</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01871274597942829</v>
+        <v>0.008765035308897495</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007353690452873707</v>
+        <v>0.001454907585866749</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01279010158032179</v>
+        <v>0.001992260804399848</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000998207600787282</v>
+        <v>0.003694254904985428</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002090171212330461</v>
+        <v>0.003072499763220549</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002396916737779975</v>
+        <v>3.708603617269546e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0150246936827898</v>
+        <v>3.568458487279713e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03098365664482117</v>
+        <v>0.01005617622286081</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0006380101549439132</v>
+        <v>0.002178932307288051</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01892995461821556</v>
+        <v>0.01205522753298283</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01283747982233763</v>
+        <v>0.002731280634179711</v>
       </c>
       <c r="O7" t="n">
-        <v>0.019154267385602</v>
+        <v>0.001051582046784461</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002260340843349695</v>
+        <v>0.004264605697244406</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001538039650768042</v>
+        <v>0.000114638009108603</v>
       </c>
       <c r="R7" t="n">
-        <v>0.004503856413066387</v>
+        <v>6.806815508753061e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008185164770111442</v>
+        <v>8.295442967209965e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.004650778137147427</v>
+        <v>0.0004916262114420533</v>
       </c>
       <c r="U7" t="n">
-        <v>0.003158505307510495</v>
+        <v>0.0006458807620219886</v>
       </c>
       <c r="V7" t="n">
-        <v>0.006978957913815975</v>
+        <v>4.951797745889053e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.005503055173903704</v>
+        <v>0.0009498157305642962</v>
       </c>
       <c r="X7" t="n">
-        <v>0.003413858823478222</v>
+        <v>0.001507859211415052</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.005524854175746441</v>
+        <v>0.001359410583972931</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002823147224262357</v>
+        <v>0.002042983658611774</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.004707794636487961</v>
+        <v>0.001983743859454989</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00155320018529892</v>
+        <v>5.916011286899447e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.009246706962585449</v>
+        <v>3.93787631765008e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001582579337991774</v>
+        <v>0.0007802796899341047</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001115871244110167</v>
+        <v>0.002171289641410112</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004690067376941442</v>
+        <v>0.0008293297723866999</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001673018559813499</v>
+        <v>0.002112692920491099</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.001157126040197909</v>
+        <v>0.0009347659070044756</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0009389698971062899</v>
+        <v>0.0002968054614029825</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001711264485493302</v>
+        <v>0.0004201562260277569</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.004308987408876419</v>
+        <v>0.0003036285343114287</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.005047379992902279</v>
+        <v>0.002347792498767376</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001003169803880155</v>
+        <v>0.001301350770518184</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.002248701639473438</v>
+        <v>0.002317097038030624</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.004084438551217318</v>
+        <v>0.001097977161407471</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.005848766304552555</v>
+        <v>0.001964129041880369</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.000192031788174063</v>
+        <v>0.0006417840486392379</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0005876008654013276</v>
+        <v>0.0005480003310367465</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.003304399782791734</v>
+        <v>0.0002441970573272556</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0004964619292877614</v>
+        <v>0.0003731396573130041</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.03341881558299065</v>
+        <v>0.004888824187219143</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.000884064647834748</v>
+        <v>0.00018237745098304</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.003423321060836315</v>
+        <v>0.00436547864228487</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.003440529108047485</v>
+        <v>0.00653592636808753</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001506834872998297</v>
+        <v>0.001410239026881754</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001309146406129003</v>
+        <v>0.0004891890566796064</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.00140665820799768</v>
+        <v>0.0009069572552107275</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.005804335698485374</v>
+        <v>0.001012794673442841</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.005144141614437103</v>
+        <v>0.0005583542515523732</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.008338067680597305</v>
+        <v>0.0009716071654111147</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.007273061666637659</v>
+        <v>0.001430210424587131</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.002167194848880172</v>
+        <v>0.0008100525592453778</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01273408066481352</v>
+        <v>0.002833049511536956</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.007250393275171518</v>
+        <v>0.0009819709230214357</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.003158980282023549</v>
+        <v>0.0009013492381200194</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.004153651650995016</v>
+        <v>0.002918644342571497</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0006503391778096557</v>
+        <v>0.001186980749480426</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.003567385254427791</v>
+        <v>0.000463743694126606</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.004722492303699255</v>
+        <v>0.0003960423055104911</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.00164468155708164</v>
+        <v>0.0003018070128746331</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.006718330550938845</v>
+        <v>0.001437762985005975</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.003650496248155832</v>
+        <v>0.0007657702080905437</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.003484690329059958</v>
+        <v>0.0006066385540179908</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.003721647197380662</v>
+        <v>2.265638613607734e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0003872410743497312</v>
+        <v>0.0005306924576871097</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.003647868055850267</v>
+        <v>0.0001268855994567275</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0001211814087582752</v>
+        <v>9.548407979309559e-05</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.01547759585082531</v>
+        <v>0.003125245217233896</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.003116034436970949</v>
+        <v>0.0006823945441283286</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.004515847656875849</v>
+        <v>0.003426739946007729</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.003944436088204384</v>
+        <v>0.001100861001759768</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.007623751647770405</v>
+        <v>0.001761596649885178</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.001596835092641413</v>
+        <v>0.001783116022124887</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0007627077866345644</v>
+        <v>0.0003824309387709945</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.004295964259654284</v>
+        <v>0.00118859380017966</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.003018047427758574</v>
+        <v>6.041384767740965e-05</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.00835881382226944</v>
+        <v>0.00318507244810462</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.003167048562318087</v>
+        <v>0.0005150407087057829</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.001117721549235284</v>
+        <v>0.003261183388531208</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.001834821072407067</v>
+        <v>0.0004331979143898934</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.003788364119827747</v>
+        <v>9.389677870785818e-05</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001326210796833038</v>
+        <v>5.406578566180542e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0004226708551868796</v>
+        <v>0.0001172305637737736</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.001594136352650821</v>
+        <v>0.0002694469003472477</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.003347980324178934</v>
+        <v>0.0006925425259396434</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0001658957917243242</v>
+        <v>0.003057294525206089</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.004790054634213448</v>
+        <v>0.002938587218523026</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.006646744441241026</v>
+        <v>0.004095807205885649</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.004083591513335705</v>
+        <v>0.0004279248823877424</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.004664166830480099</v>
+        <v>0.001168924616649747</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.003388748271390796</v>
+        <v>0.0007889387779869139</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.004130909219384193</v>
+        <v>0.001142294029705226</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.001517609460279346</v>
+        <v>0.0008510940242558718</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.002475100103765726</v>
+        <v>8.59463689266704e-05</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.006569864228367805</v>
+        <v>0.003206536639481783</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.002992428373545408</v>
+        <v>0.0006448145722970366</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.003544334089383483</v>
+        <v>0.003500388003885746</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.001957102678716183</v>
+        <v>0.0008465173887088895</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.004496348556131124</v>
+        <v>9.824566222960129e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.001695811515673995</v>
+        <v>0.0001212958595715463</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0006260422524064779</v>
+        <v>0.0001712245866656303</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.001053637126460671</v>
+        <v>0.00054492789786309</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.005704057868570089</v>
+        <v>0.001138930441811681</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.00283476896584034</v>
+        <v>0.001768101705238223</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.002074589719995856</v>
+        <v>3.84728773497045e-05</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.008092693984508514</v>
+        <v>0.002759895753115416</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.006417172029614449</v>
+        <v>0.0004874195146840066</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0006837413529865444</v>
+        <v>0.003188961884006858</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.002522854600101709</v>
+        <v>0.0006642239750362933</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.000823465408757329</v>
+        <v>0.003798827761784196</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0007959709037095308</v>
+        <v>0.001448306022211909</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.005083735100924969</v>
+        <v>0.0001358029549010098</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.001819520373828709</v>
+        <v>0.001651782891713083</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.004291539080440998</v>
+        <v>0.0005395550397224724</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0003304334240965545</v>
+        <v>0.001997231971472502</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.001092620310373604</v>
+        <v>0.0001289026404265314</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.00675984937697649</v>
+        <v>0.0006547056254930794</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.000661770231090486</v>
+        <v>0.002432295819744468</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.001220718142576516</v>
+        <v>0.0007106935372576118</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.002390509704127908</v>
+        <v>0.00384886097162962</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.002683232538402081</v>
+        <v>6.806102464906871e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0001572366163600236</v>
+        <v>0.0006907236529514194</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.008515625260770321</v>
+        <v>0.0009687147103250027</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.002581855282187462</v>
+        <v>0.001725529204122722</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.005511761177331209</v>
+        <v>0.00110146077349782</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0006500793970189989</v>
+        <v>0.002113450318574905</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0004838371824007481</v>
+        <v>9.246485569747165e-05</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0009843312436714768</v>
+        <v>0.005141966976225376</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.003146046306937933</v>
+        <v>0.003263395978137851</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0001012731809169054</v>
+        <v>0.001153028337284923</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.004250977654010057</v>
+        <v>0.002128529595211148</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0001340199378319085</v>
+        <v>0.0009157692547887564</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0001684500020928681</v>
+        <v>0.002906028646975756</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0002392923342995346</v>
+        <v>0.0008863412658683956</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.002289786003530025</v>
+        <v>0.0001386856893077493</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.002501562004908919</v>
+        <v>0.0003646960249170661</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0009444323368370533</v>
+        <v>8.169756620191038e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>7.755344267934561e-05</v>
+        <v>0.0003252141759730875</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.003265243489295244</v>
+        <v>0.0009140745969489217</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.007154325488954782</v>
+        <v>0.003017062786966562</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.001753302058205009</v>
+        <v>1.677218824625015e-05</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.004199613817036152</v>
+        <v>0.00181952805723995</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.005253963638097048</v>
+        <v>0.0008848991710692644</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.01271477807313204</v>
+        <v>0.0005070981569588184</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.003347849473357201</v>
+        <v>0.001528953784145415</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.006112020928412676</v>
+        <v>0.000550961762201041</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.001202260260470212</v>
+        <v>0.002129684668034315</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.001892006723210216</v>
+        <v>0.0001041790965246037</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.006931561511009932</v>
+        <v>0.003406916512176394</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0007583671831525862</v>
+        <v>0.0004305322363507003</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.002376982709392905</v>
+        <v>0.003707371419295669</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.001539261313155293</v>
+        <v>0.0005138196283951402</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.004798147827386856</v>
+        <v>0.0002507076424080878</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.002077148761600256</v>
+        <v>0.0003460553416516632</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0006405276944860816</v>
+        <v>0.000504696334246546</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.002029714873060584</v>
+        <v>0.0006545283831655979</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.001429219148121774</v>
+        <v>0.0002604128676466644</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.002947454806417227</v>
+        <v>0.001008592080324888</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.002280612476170063</v>
+        <v>0.0008991624345071614</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.004997802432626486</v>
+        <v>0.001529418863356113</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.001571888453327119</v>
+        <v>0.001376463449560106</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.001765840221196413</v>
+        <v>0.001421243185177445</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.001612978288903832</v>
+        <v>0.0009792170021682978</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.004069521557539701</v>
+        <v>0.002477838192135096</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.006616830825805664</v>
+        <v>0.000611851632129401</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.003251183778047562</v>
+        <v>0.002394587267190218</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.005236636381596327</v>
+        <v>0.003442565444856882</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.003012689528986812</v>
+        <v>0.0004073382588103414</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.004063725005835295</v>
+        <v>0.002405006438493729</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01417955942451954</v>
+        <v>0.002869096118956804</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.004688437562435865</v>
+        <v>0.002439933829009533</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0006662225350737572</v>
+        <v>0.001110548386350274</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.002518803346902132</v>
+        <v>0.0005622087046504021</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.00278389360755682</v>
+        <v>0.003299332223832607</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.005505022592842579</v>
+        <v>0.001050188555382192</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.003372046397998929</v>
+        <v>0.00110357953235507</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.003677301341667771</v>
+        <v>0.0005707896780222654</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.001925599295645952</v>
+        <v>0.003130110213533044</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.004976941738277674</v>
+        <v>0.002626216504722834</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.002801233669742942</v>
+        <v>0.0005537333781830966</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.01060112379491329</v>
+        <v>0.003432929515838623</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0001824531937018037</v>
+        <v>0.0003757125814445317</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.001842366298660636</v>
+        <v>0.0005013826303184032</v>
       </c>
     </row>
     <row r="8">
@@ -4982,1140 +4982,1140 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0004258544649928808</v>
+        <v>0.0004817182198166847</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00151656090747565</v>
+        <v>0.1005513519048691</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001469698618166149</v>
+        <v>0.02185845747590065</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0006376969395205379</v>
+        <v>0.01805021800100803</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004557188658509403</v>
+        <v>0.001184698194265366</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0005719829350709915</v>
+        <v>0.06160654127597809</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002866685972549021</v>
+        <v>0.04040407761931419</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0001106249910662882</v>
+        <v>0.04370678588747978</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001928987476276234</v>
+        <v>0.02858213894069195</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003787971800193191</v>
+        <v>0.02380309998989105</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001006391132250428</v>
+        <v>0.1004419177770615</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001472193980589509</v>
+        <v>0.01614973694086075</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0008499374380335212</v>
+        <v>0.04855289310216904</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0006197098991833627</v>
+        <v>0.03736103698611259</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0007283980958163738</v>
+        <v>0.06523333489894867</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0004115935298614204</v>
+        <v>0.01859350502490997</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0004190234176348895</v>
+        <v>0.01400084234774113</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001059106798493303</v>
+        <v>0.05500752478837967</v>
       </c>
       <c r="S9" t="n">
-        <v>4.704211460193619e-05</v>
+        <v>0.008485384285449982</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0003005140752065927</v>
+        <v>0.05117093771696091</v>
       </c>
       <c r="U9" t="n">
-        <v>5.751228673034348e-05</v>
+        <v>0.00572561752051115</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001272555236937478</v>
+        <v>0.02428699657320976</v>
       </c>
       <c r="W9" t="n">
-        <v>6.859382119728252e-05</v>
+        <v>0.01994960941374302</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0002080661506624892</v>
+        <v>0.01836999133229256</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0001052348525263369</v>
+        <v>0.00437976373359561</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.311526597826742e-06</v>
+        <v>0.005936904344707727</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.96525671123527e-05</v>
+        <v>0.01202825177460909</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.723439582856372e-05</v>
+        <v>0.004448531195521355</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0002924934378825128</v>
+        <v>0.001379851251840591</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0002005381393246353</v>
+        <v>0.02205696329474449</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0004280424909666181</v>
+        <v>0.04630061611533165</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0001915619650389999</v>
+        <v>0.03672706335783005</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.054531250905711e-05</v>
+        <v>0.02413923293352127</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0002120804565493017</v>
+        <v>0.008138220757246017</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.299523086752743e-06</v>
+        <v>0.06565608084201813</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0001155326317530125</v>
+        <v>0.008266538381576538</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0002290838165208697</v>
+        <v>0.002276026643812656</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0002561921428423375</v>
+        <v>0.03892562538385391</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.836754199757706e-05</v>
+        <v>0.005255751311779022</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.206641511293128e-06</v>
+        <v>0.01995178684592247</v>
       </c>
       <c r="AO9" t="n">
-        <v>6.720482633681968e-05</v>
+        <v>0.01955381408333778</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0001761274470482022</v>
+        <v>0.02276812121272087</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0001594347559148446</v>
+        <v>0.001640591770410538</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0001027247999445535</v>
+        <v>0.05853311717510223</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.844497304176912e-05</v>
+        <v>0.008670521900057793</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0001905081735458225</v>
+        <v>0.00478079728782177</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.001267263200134039</v>
+        <v>0.128642737865448</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.630728603340685e-05</v>
+        <v>0.002737214788794518</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.959135837154463e-05</v>
+        <v>0.001569054205901921</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0001747385831549764</v>
+        <v>0.005546706262975931</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0001660908164922148</v>
+        <v>0.05527469143271446</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0003184124652761966</v>
+        <v>0.006406967528164387</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.548546035541221e-05</v>
+        <v>0.02837250009179115</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.193583663436584e-05</v>
+        <v>0.01944926008582115</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0001834799768403172</v>
+        <v>0.002321802079677582</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0002309472329216078</v>
+        <v>0.03959730267524719</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0002095178788295016</v>
+        <v>0.0291092824190855</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.072414155118167e-05</v>
+        <v>0.02926484495401382</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.000608104863204062</v>
+        <v>0.06039279326796532</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.000253130798228085</v>
+        <v>0.01921681500971317</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0001190305920317769</v>
+        <v>0.02051136083900928</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0003154552832711488</v>
+        <v>0.007328792009502649</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0002028158487519249</v>
+        <v>0.0277105700224638</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0001351422106381506</v>
+        <v>0.01014134287834167</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0002576452388893813</v>
+        <v>0.01130834687501192</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.344454595819116e-05</v>
+        <v>0.01160098426043987</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.000305521214613691</v>
+        <v>0.02538859099149704</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0002780763024929911</v>
+        <v>0.01237006857991219</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.254423740552738e-07</v>
+        <v>0.01899725943803787</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0002243283379357308</v>
+        <v>0.03037075325846672</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.394033279211726e-05</v>
+        <v>0.01001172326505184</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.531327380798757e-05</v>
+        <v>0.02044293284416199</v>
       </c>
       <c r="BU9" t="n">
-        <v>7.51282277633436e-05</v>
+        <v>0.01626226492226124</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.000516423606313765</v>
+        <v>0.121185764670372</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.01035382412374e-05</v>
+        <v>0.01461654808372259</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0001610086765140295</v>
+        <v>0.02204874530434608</v>
       </c>
       <c r="BY9" t="n">
-        <v>8.950541814556345e-05</v>
+        <v>0.0267414003610611</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.000245898001594469</v>
+        <v>0.006419846322387457</v>
       </c>
       <c r="CA9" t="n">
-        <v>6.626738468185067e-05</v>
+        <v>0.02518871240317822</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0001050140708684921</v>
+        <v>0.001924325712025166</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.642669955501333e-05</v>
+        <v>0.0008324314840137959</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.769378185505047e-05</v>
+        <v>0.006748745683580637</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0003122377092950046</v>
+        <v>0.03948521614074707</v>
       </c>
       <c r="CF9" t="n">
-        <v>6.858172855572775e-05</v>
+        <v>0.006048922426998615</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0001239362318301573</v>
+        <v>0.006043559871613979</v>
       </c>
       <c r="CH9" t="n">
-        <v>4.219688707962632e-05</v>
+        <v>0.006479346659034491</v>
       </c>
       <c r="CI9" t="n">
-        <v>9.659393253969029e-05</v>
+        <v>0.01133318245410919</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001139724627137184</v>
+        <v>0.004338999278843403</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.847951716626994e-05</v>
+        <v>0.005383652169257402</v>
       </c>
       <c r="CL9" t="n">
-        <v>5.186738417251036e-05</v>
+        <v>0.002392116235569119</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0002669363166205585</v>
+        <v>0.01749686151742935</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0002167769416701049</v>
+        <v>0.06915637850761414</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0001781019527697936</v>
+        <v>0.003583315759897232</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0001922932715388015</v>
+        <v>0.02584359608590603</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0001911844010464847</v>
+        <v>0.03842728585004807</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0003080300521105528</v>
+        <v>0.00372530659660697</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.254920243809465e-05</v>
+        <v>0.02766036614775658</v>
       </c>
       <c r="CT9" t="n">
-        <v>9.080316522158682e-05</v>
+        <v>0.02661767229437828</v>
       </c>
       <c r="CU9" t="n">
-        <v>3.731203469214961e-05</v>
+        <v>0.005869511980563402</v>
       </c>
       <c r="CV9" t="n">
-        <v>4.502571755438112e-05</v>
+        <v>0.001425393391400576</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0002343773230677471</v>
+        <v>0.03632266074419022</v>
       </c>
       <c r="CX9" t="n">
-        <v>6.40864236629568e-05</v>
+        <v>0.006319453008472919</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0001964702532859519</v>
+        <v>0.003980007953941822</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.221866270701867e-05</v>
+        <v>0.007237355224788189</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0001321892341366038</v>
+        <v>0.01257530692964792</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0001319208386121318</v>
+        <v>0.004515670239925385</v>
       </c>
       <c r="DC9" t="n">
-        <v>5.237707955529913e-05</v>
+        <v>0.003507206914946437</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.282211037003435e-05</v>
+        <v>0.0007195370271801949</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0001035835957736708</v>
+        <v>0.02076718956232071</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0004458418115973473</v>
+        <v>0.06970030069351196</v>
       </c>
       <c r="DG9" t="n">
-        <v>9.180314373224974e-05</v>
+        <v>0.02809569239616394</v>
       </c>
       <c r="DH9" t="n">
-        <v>6.596879393327981e-05</v>
+        <v>0.02057241275906563</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0004752922977786511</v>
+        <v>0.02475592121481895</v>
       </c>
       <c r="DJ9" t="n">
-        <v>4.055798490298912e-05</v>
+        <v>0.05570920556783676</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.000373650633264333</v>
+        <v>0.01958638615906239</v>
       </c>
       <c r="DL9" t="n">
-        <v>7.095831824699417e-05</v>
+        <v>0.04499876499176025</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0001649330952204764</v>
+        <v>0.03032942302525043</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0002371634473092854</v>
+        <v>0.004876465070992708</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001952016173163429</v>
+        <v>0.01329283136874437</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0001233010989381</v>
+        <v>0.005876522976905107</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.000264049245743081</v>
+        <v>0.03562376275658607</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0001038033733493648</v>
+        <v>0.01270513888448477</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0001515752519480884</v>
+        <v>0.006372491829097271</v>
       </c>
       <c r="DT9" t="n">
-        <v>7.03932746546343e-05</v>
+        <v>0.007524711545556784</v>
       </c>
       <c r="DU9" t="n">
-        <v>6.141026096884161e-05</v>
+        <v>0.006028271280229092</v>
       </c>
       <c r="DV9" t="n">
-        <v>9.138627501670271e-05</v>
+        <v>0.002277769381180406</v>
       </c>
       <c r="DW9" t="n">
-        <v>3.571778506739065e-05</v>
+        <v>0.009203583002090454</v>
       </c>
       <c r="DX9" t="n">
-        <v>8.501021511619911e-05</v>
+        <v>0.03102738223969936</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0002401776582701132</v>
+        <v>0.02148786000907421</v>
       </c>
       <c r="DZ9" t="n">
-        <v>7.162777183111757e-05</v>
+        <v>0.009204554371535778</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0001696607650956139</v>
+        <v>0.01736969687044621</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0001003002325887792</v>
+        <v>0.008872766979038715</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.376547490712255e-05</v>
+        <v>0.00271649332717061</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0001832199923228472</v>
+        <v>0.02926292270421982</v>
       </c>
       <c r="EE9" t="n">
-        <v>7.361453754128888e-05</v>
+        <v>0.02957972697913647</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0001288801722694188</v>
+        <v>0.003077917033806443</v>
       </c>
       <c r="EG9" t="n">
-        <v>1.379499735776335e-05</v>
+        <v>0.009395202621817589</v>
       </c>
       <c r="EH9" t="n">
-        <v>2.935959855676629e-05</v>
+        <v>0.004585145972669125</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0001352900872007012</v>
+        <v>0.02374893799424171</v>
       </c>
       <c r="EJ9" t="n">
-        <v>3.561499033821747e-05</v>
+        <v>0.008350263349711895</v>
       </c>
       <c r="EK9" t="n">
-        <v>6.829289486631751e-05</v>
+        <v>0.01087968051433563</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001666335010668263</v>
+        <v>0.006767173763364553</v>
       </c>
       <c r="EM9" t="n">
-        <v>2.022420812863857e-05</v>
+        <v>0.01507880259305239</v>
       </c>
       <c r="EN9" t="n">
-        <v>3.118879249086604e-05</v>
+        <v>0.001288774888962507</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0002013749035540968</v>
+        <v>0.01359893474727869</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0001482191728428006</v>
+        <v>0.02555252611637115</v>
       </c>
       <c r="EQ9" t="n">
-        <v>3.272022149758413e-05</v>
+        <v>0.001560462173074484</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0001342292380286381</v>
+        <v>0.02452278137207031</v>
       </c>
       <c r="ES9" t="n">
-        <v>3.274669870734215e-05</v>
+        <v>0.05599022284150124</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0003629488637670875</v>
+        <v>0.006632721051573753</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0001873469154816121</v>
+        <v>0.01028191857039928</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.000241546455072239</v>
+        <v>0.02249863743782043</v>
       </c>
       <c r="EW9" t="n">
-        <v>2.881507862184662e-05</v>
+        <v>0.005403293296694756</v>
       </c>
       <c r="EX9" t="n">
-        <v>4.697895565186627e-05</v>
+        <v>0.005493533797562122</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.000220458023250103</v>
+        <v>0.04442713409662247</v>
       </c>
       <c r="EZ9" t="n">
-        <v>3.652840405266033e-06</v>
+        <v>0.00247450708411634</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0001444087538402528</v>
+        <v>0.0007921662181615829</v>
       </c>
       <c r="FB9" t="n">
-        <v>3.356487286509946e-05</v>
+        <v>0.008539487607777119</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0001493785239290446</v>
+        <v>0.01145496405661106</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0001323484029853716</v>
+        <v>0.002102692145854235</v>
       </c>
       <c r="FE9" t="n">
-        <v>1.982711182790808e-05</v>
+        <v>0.0009367275051772594</v>
       </c>
       <c r="FF9" t="n">
-        <v>5.883148696739227e-05</v>
+        <v>0.005841208156198263</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0001701706642052159</v>
+        <v>0.01431652158498764</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0001916469191201031</v>
+        <v>0.02229248732328415</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.00010487693361938</v>
+        <v>0.003025725483894348</v>
       </c>
       <c r="FJ9" t="n">
-        <v>6.888022471684963e-05</v>
+        <v>0.0226932130753994</v>
       </c>
       <c r="FK9" t="n">
-        <v>4.534409163170494e-05</v>
+        <v>0.004209044389426708</v>
       </c>
       <c r="FL9" t="n">
-        <v>5.39328102604486e-05</v>
+        <v>0.03675882518291473</v>
       </c>
       <c r="FM9" t="n">
-        <v>3.693166217999533e-05</v>
+        <v>0.01447277516126633</v>
       </c>
       <c r="FN9" t="n">
-        <v>6.647210830124095e-05</v>
+        <v>0.03317495435476303</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001187651796499267</v>
+        <v>0.02472073771059513</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.000198991212528199</v>
+        <v>0.01159980241209269</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0002333442389499396</v>
+        <v>0.01710995100438595</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0002566185430623591</v>
+        <v>0.01430325955152512</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.00014134643424768</v>
+        <v>0.003226516768336296</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0005245179054327309</v>
+        <v>0.05656407028436661</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0003392415819689631</v>
+        <v>0.0409964956343174</v>
       </c>
       <c r="FV9" t="n">
-        <v>9.70703549683094e-05</v>
+        <v>0.02888575382530689</v>
       </c>
       <c r="FW9" t="n">
-        <v>8.893063204595819e-05</v>
+        <v>0.04363586381077766</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0001152378972619772</v>
+        <v>0.007049530744552612</v>
       </c>
       <c r="FY9" t="n">
-        <v>7.548858411610126e-05</v>
+        <v>0.01223007123917341</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0003204475506208837</v>
+        <v>0.02289900742471218</v>
       </c>
       <c r="GA9" t="n">
-        <v>1.288768817175878e-05</v>
+        <v>0.008761696517467499</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.000272472680080682</v>
+        <v>0.01346970908343792</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0001341932656941935</v>
+        <v>0.009742210619151592</v>
       </c>
       <c r="GD9" t="n">
-        <v>8.452955808024853e-05</v>
+        <v>0.02855342626571655</v>
       </c>
       <c r="GE9" t="n">
-        <v>9.152410348178819e-05</v>
+        <v>0.0008094478398561478</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0002005388669203967</v>
+        <v>0.0296257846057415</v>
       </c>
       <c r="GG9" t="n">
-        <v>8.723649443709292e-06</v>
+        <v>0.01955564320087433</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0002554201346356422</v>
+        <v>0.00204105768352747</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001933258608914912</v>
+        <v>0.0116162495687604</v>
       </c>
       <c r="C10" t="n">
-        <v>9.472017700318247e-05</v>
+        <v>0.002308258786797523</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0008546625613234937</v>
+        <v>0.009243689477443695</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0004462434444576502</v>
+        <v>0.002019739942625165</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0004316592821851373</v>
+        <v>0.008218548260629177</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001555760245537385</v>
+        <v>0.004807425197213888</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0001668048207648098</v>
+        <v>0.004967388696968555</v>
       </c>
       <c r="I10" t="n">
-        <v>6.172934809001163e-05</v>
+        <v>0.0009624905651435256</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003665967960841954</v>
+        <v>0.001861782744526863</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001240702229551971</v>
+        <v>0.01151230931282043</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0001234559022122994</v>
+        <v>0.004443113692104816</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0009062357130460441</v>
+        <v>0.01307930052280426</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0008899269159883261</v>
+        <v>0.004515293054282665</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0007275561220012605</v>
+        <v>0.007240270264446735</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0001148328301496804</v>
+        <v>0.005849611945450306</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0001238649128936231</v>
+        <v>0.001818216638639569</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001079665962606668</v>
+        <v>0.001427071169018745</v>
       </c>
       <c r="S10" t="n">
-        <v>5.536824755836278e-05</v>
+        <v>0.001125652925111353</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0003484105400275439</v>
+        <v>7.227617606986314e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>3.673848550533876e-05</v>
+        <v>0.0007317699491977692</v>
       </c>
       <c r="V10" t="n">
-        <v>0.000249070959398523</v>
+        <v>1.082458857126767e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0001710022334009409</v>
+        <v>0.001427410170435905</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0002328236732864752</v>
+        <v>0.003393802093341947</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002098508266499266</v>
+        <v>0.0006169189582578838</v>
       </c>
       <c r="Z10" t="n">
-        <v>8.887321018846706e-05</v>
+        <v>0.002076314529404044</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0001246547035407275</v>
+        <v>0.002074020449072123</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0001563710102345794</v>
+        <v>0.001830181339755654</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0002610859519336373</v>
+        <v>0.001910649007186294</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0001054981112247333</v>
+        <v>0.002260910114273429</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.531270027044229e-05</v>
+        <v>0.0001194567885249853</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0001844408689066768</v>
+        <v>0.000970796390902251</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.66655575716868e-05</v>
+        <v>0.005177346989512444</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.405471215955913e-05</v>
+        <v>0.0001197362435050309</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.156562161166221e-05</v>
+        <v>0.002474571112543344</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.0548609578982e-05</v>
+        <v>0.001265686354599893</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0001607240265002474</v>
+        <v>0.001162701286375523</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0002134655369445682</v>
+        <v>0.004047543741762638</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.852028268942377e-06</v>
+        <v>0.002729004481807351</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.27292785490863e-05</v>
+        <v>0.002058558864519</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0002365758409723639</v>
+        <v>0.000908179092220962</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0002734837180469185</v>
+        <v>0.002685496117919683</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.972565951291472e-05</v>
+        <v>0.00179764605127275</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.254242983530276e-05</v>
+        <v>0.0003956557775381953</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0001142104738391936</v>
+        <v>0.0008114882512018085</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0001834812865126878</v>
+        <v>0.0009679816430434585</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.00143693364225328</v>
+        <v>0.006700403522700071</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.130286884494126e-05</v>
+        <v>0.002362489933148026</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0001496952609159052</v>
+        <v>0.004901519045233727</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0002281361521454528</v>
+        <v>0.008681423962116241</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.24698144645663e-05</v>
+        <v>0.006003769114613533</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0001112827667384408</v>
+        <v>0.0001814802817534655</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.910821058321744e-05</v>
+        <v>2.085027517750859e-06</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.093175837420858e-05</v>
+        <v>0.00102163152769208</v>
       </c>
       <c r="BC10" t="n">
-        <v>9.153717110166326e-05</v>
+        <v>0.001504517393186688</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0003163715300615877</v>
+        <v>0.0003592011053115129</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0002687149972189218</v>
+        <v>0.002292164601385593</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0001316421403316781</v>
+        <v>0.001432756311260164</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.000626243359874934</v>
+        <v>0.003553448477759957</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0003927407960873097</v>
+        <v>0.001068640034645796</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0002370804140809923</v>
+        <v>0.001437389524653554</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0001046237157424912</v>
+        <v>0.002757057081907988</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.011703979107551e-05</v>
+        <v>0.001779922633431852</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0002772693987935781</v>
+        <v>0.0007162683177739382</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0003319572715554386</v>
+        <v>0.0002286467351950705</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.816421253257431e-05</v>
+        <v>2.756057801889256e-05</v>
       </c>
       <c r="BO10" t="n">
-        <v>9.692746243672445e-05</v>
+        <v>0.001869490602985024</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0003025602491106838</v>
+        <v>0.0005227194633334875</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0002041509578702971</v>
+        <v>0.0004079099162481725</v>
       </c>
       <c r="BR10" t="n">
-        <v>8.813659951556474e-05</v>
+        <v>0.0002910142648033798</v>
       </c>
       <c r="BS10" t="n">
-        <v>5.339740528143011e-05</v>
+        <v>0.001121834735386074</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0001643155119381845</v>
+        <v>0.0005455179489217699</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0001445152593078092</v>
+        <v>0.0001981150708161294</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0007370630046352744</v>
+        <v>0.004466813057661057</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.714834646321833e-05</v>
+        <v>0.001508937566541135</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0001373595005134121</v>
+        <v>0.005483022890985012</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.702563016209751e-05</v>
+        <v>0.002008427865803242</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0003447943308856338</v>
+        <v>0.004103985615074635</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.163844278082252e-05</v>
+        <v>0.001031149877235293</v>
       </c>
       <c r="CB10" t="n">
-        <v>9.957193105947226e-05</v>
+        <v>0.0004370892711449414</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0001258615520782769</v>
+        <v>0.001664764829911292</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0001440707710571587</v>
+        <v>9.243344538845122e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0003191879077348858</v>
+        <v>0.003913639578968287</v>
       </c>
       <c r="CF10" t="n">
-        <v>9.738165681483224e-05</v>
+        <v>0.0003425536851864308</v>
       </c>
       <c r="CG10" t="n">
-        <v>7.638313400093466e-05</v>
+        <v>0.00359109346754849</v>
       </c>
       <c r="CH10" t="n">
-        <v>3.572559580788948e-05</v>
+        <v>5.625643098028377e-07</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0001035796376527287</v>
+        <v>0.001575248665176332</v>
       </c>
       <c r="CJ10" t="n">
-        <v>4.882965004071593e-05</v>
+        <v>0.0003708484582602978</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.35939299070742e-05</v>
+        <v>0.0008217931026592851</v>
       </c>
       <c r="CL10" t="n">
-        <v>5.751432399847545e-05</v>
+        <v>1.490251452196389e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0002078368852380663</v>
+        <v>0.0007523640524595976</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0001835893344832584</v>
+        <v>0.001929443445987999</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.000107996427686885</v>
+        <v>0.004831405356526375</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0003509553789626807</v>
+        <v>0.005149243399500847</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0002998685231432319</v>
+        <v>0.0005217696889303625</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0002024346322286874</v>
+        <v>0.0012564726639539</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0001787391374818981</v>
+        <v>0.0008635994745418429</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0002925481821876019</v>
+        <v>0.001474929857067764</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.354087453364627e-05</v>
+        <v>0.00071129878051579</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0001242465950781479</v>
+        <v>1.401396002620459e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0002475104993209243</v>
+        <v>0.00372754642739892</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0001096094856620766</v>
+        <v>0.0008149056229740381</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0001620938710402697</v>
+        <v>0.003918442875146866</v>
       </c>
       <c r="CZ10" t="n">
-        <v>3.963846756960265e-05</v>
+        <v>0.0009443438029848039</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0001236835814779624</v>
+        <v>0.001781723811291158</v>
       </c>
       <c r="DB10" t="n">
-        <v>6.060966188670136e-05</v>
+        <v>0.0006008471827954054</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.975802999571897e-05</v>
+        <v>0.0006803305586799979</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.362189793027937e-05</v>
+        <v>0.0002894049976021051</v>
       </c>
       <c r="DE10" t="n">
-        <v>6.697494245599955e-05</v>
+        <v>0.0006297293584793806</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0003155352897010744</v>
+        <v>0.003561046905815601</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.533446215442382e-05</v>
+        <v>0.001052036066539586</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0003023584431502968</v>
+        <v>0.002954993862658739</v>
       </c>
       <c r="DI10" t="n">
-        <v>8.702307241037488e-05</v>
+        <v>0.0007528411806561053</v>
       </c>
       <c r="DJ10" t="n">
-        <v>5.648224760079756e-05</v>
+        <v>0.007496165111660957</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0001172984266304411</v>
+        <v>0.001312713953666389</v>
       </c>
       <c r="DL10" t="n">
-        <v>3.699368244269863e-05</v>
+        <v>0.006493495311588049</v>
       </c>
       <c r="DM10" t="n">
-        <v>8.695494761923328e-05</v>
+        <v>0.002650935901328921</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0002046176668955013</v>
+        <v>0.0007313218084163964</v>
       </c>
       <c r="DO10" t="n">
-        <v>6.632119766436517e-05</v>
+        <v>0.001954244915395975</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0001161317341029644</v>
+        <v>0.0003837755066342652</v>
       </c>
       <c r="DQ10" t="n">
-        <v>9.719307854538783e-05</v>
+        <v>0.0009033118840306997</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.977368659339845e-05</v>
+        <v>0.0001339995651505888</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0002442709519527853</v>
+        <v>0.001380296191200614</v>
       </c>
       <c r="DT10" t="n">
-        <v>7.239053957164288e-05</v>
+        <v>0.001345328986644745</v>
       </c>
       <c r="DU10" t="n">
-        <v>1.850860644481145e-05</v>
+        <v>0.00232748594135046</v>
       </c>
       <c r="DV10" t="n">
-        <v>7.757174898870289e-05</v>
+        <v>0.005091058555990458</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0001529233122710139</v>
+        <v>0.0001685819588601589</v>
       </c>
       <c r="DX10" t="n">
-        <v>4.46263984485995e-05</v>
+        <v>0.0003922969626728445</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0002908609458245337</v>
+        <v>0.002443706849589944</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0001015876041492447</v>
+        <v>0.001483027823269367</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0002231372491223738</v>
+        <v>0.0003203086089342833</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0001028896949719638</v>
+        <v>0.003756401594728231</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.952678212546743e-05</v>
+        <v>0.0004553741309791803</v>
       </c>
       <c r="ED10" t="n">
-        <v>6.191922147991136e-05</v>
+        <v>0.0058229835703969</v>
       </c>
       <c r="EE10" t="n">
-        <v>2.289797157573048e-05</v>
+        <v>0.005511907394975424</v>
       </c>
       <c r="EF10" t="n">
-        <v>4.221743438392878e-05</v>
+        <v>0.00187676539644599</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0001474918681196868</v>
+        <v>0.002483424730598927</v>
       </c>
       <c r="EH10" t="n">
-        <v>1.185788005386712e-05</v>
+        <v>0.002201026305556297</v>
       </c>
       <c r="EI10" t="n">
-        <v>6.880508590256795e-05</v>
+        <v>0.003598254639655352</v>
       </c>
       <c r="EJ10" t="n">
-        <v>7.745707989670336e-05</v>
+        <v>0.0004025563830509782</v>
       </c>
       <c r="EK10" t="n">
-        <v>9.946606587618589e-05</v>
+        <v>0.001285964855924249</v>
       </c>
       <c r="EL10" t="n">
-        <v>9.584413783159107e-05</v>
+        <v>7.458525942638516e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>4.729223292088136e-05</v>
+        <v>0.000149341460200958</v>
       </c>
       <c r="EN10" t="n">
-        <v>9.634048183215782e-06</v>
+        <v>0.0003933839034289122</v>
       </c>
       <c r="EO10" t="n">
-        <v>9.148247772827744e-05</v>
+        <v>0.001016693888232112</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0002106080501107499</v>
+        <v>0.003891728352755308</v>
       </c>
       <c r="EQ10" t="n">
-        <v>2.520075213396922e-05</v>
+        <v>9.57750016823411e-05</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0001294906105613336</v>
+        <v>0.002980529796332121</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0001497858029324561</v>
+        <v>0.0009355910588055849</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0004881607310380787</v>
+        <v>0.0007309167995117605</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0001789935922715813</v>
+        <v>0.001176249352283776</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0002055456134257838</v>
+        <v>0.001541538164019585</v>
       </c>
       <c r="EW10" t="n">
-        <v>2.782213414320722e-06</v>
+        <v>0.003122274298220873</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0001000164484139532</v>
+        <v>1.370775862596929e-06</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.0002686510269995779</v>
+        <v>0.004189301747828722</v>
       </c>
       <c r="EZ10" t="n">
-        <v>3.595216185203753e-05</v>
+        <v>0.0004142193356528878</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0001156079961219802</v>
+        <v>0.004098375327885151</v>
       </c>
       <c r="FB10" t="n">
-        <v>1.275286194868386e-05</v>
+        <v>0.0001330910599790514</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0001500622456660494</v>
+        <v>0.001678119646385312</v>
       </c>
       <c r="FD10" t="n">
-        <v>7.811730029061437e-05</v>
+        <v>0.0006987857632339001</v>
       </c>
       <c r="FE10" t="n">
-        <v>2.992819281644188e-05</v>
+        <v>0.001057653455063701</v>
       </c>
       <c r="FF10" t="n">
-        <v>7.693337101954967e-05</v>
+        <v>0.0008616075501777232</v>
       </c>
       <c r="FG10" t="n">
-        <v>6.415987445507199e-05</v>
+        <v>0.0001324052864219993</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0001399301836499944</v>
+        <v>0.001691452111117542</v>
       </c>
       <c r="FI10" t="n">
-        <v>6.491695967270061e-05</v>
+        <v>0.0003693519392982125</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0001461436186218634</v>
+        <v>0.002100538462400436</v>
       </c>
       <c r="FK10" t="n">
-        <v>3.305522113805637e-05</v>
+        <v>0.001036627683788538</v>
       </c>
       <c r="FL10" t="n">
-        <v>5.714003782486543e-05</v>
+        <v>0.0001849461114034057</v>
       </c>
       <c r="FM10" t="n">
-        <v>2.010119351325557e-05</v>
+        <v>0.0008609537617303431</v>
       </c>
       <c r="FN10" t="n">
-        <v>6.714853952871636e-05</v>
+        <v>0.000132524233777076</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0001289217034354806</v>
+        <v>0.0007194837089627981</v>
       </c>
       <c r="FP10" t="n">
-        <v>2.81819829979213e-05</v>
+        <v>0.001964270602911711</v>
       </c>
       <c r="FQ10" t="n">
-        <v>5.920386320212856e-05</v>
+        <v>0.004545619711279869</v>
       </c>
       <c r="FR10" t="n">
-        <v>2.879144085454755e-05</v>
+        <v>0.003137724474072456</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0002796005574055016</v>
+        <v>0.003683399874716997</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0002191731036873534</v>
+        <v>0.003963280469179153</v>
       </c>
       <c r="FU10" t="n">
-        <v>5.158065687282942e-05</v>
+        <v>0.001888585044071078</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0001138464358518831</v>
+        <v>0.0002182064345106483</v>
       </c>
       <c r="FW10" t="n">
-        <v>1.014780355035327e-05</v>
+        <v>0.00515100359916687</v>
       </c>
       <c r="FX10" t="n">
-        <v>9.669059363659471e-05</v>
+        <v>0.002411902416497469</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0002637908328324556</v>
+        <v>0.001417208928614855</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0001199489706777968</v>
+        <v>0.0005327838589437306</v>
       </c>
       <c r="GA10" t="n">
-        <v>4.421350604388863e-05</v>
+        <v>0.001226817141287029</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0001145424612332135</v>
+        <v>0.0036722959484905</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0001178060774691403</v>
+        <v>0.0005969226476736367</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0002776082546915859</v>
+        <v>0.002744783880189061</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0004539125366136432</v>
+        <v>0.002289187163114548</v>
       </c>
       <c r="GF10" t="n">
-        <v>3.191838186467066e-05</v>
+        <v>0.001974968239665031</v>
       </c>
       <c r="GG10" t="n">
-        <v>5.026242433814332e-05</v>
+        <v>0.001366108655929565</v>
       </c>
     </row>
     <row r="11">
@@ -6689,2278 +6689,2278 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1.774847074864638e-10</v>
+        <v>2.524315689811374e-08</v>
       </c>
       <c r="B12" t="n">
-        <v>1.726673665158884e-10</v>
+        <v>1.854238718124179e-07</v>
       </c>
       <c r="C12" t="n">
-        <v>7.630948650749758e-11</v>
+        <v>3.982932383905791e-08</v>
       </c>
       <c r="D12" t="n">
-        <v>8.601739875935266e-10</v>
+        <v>4.26890593985263e-08</v>
       </c>
       <c r="E12" t="n">
-        <v>1.049426032184719e-10</v>
+        <v>4.278619769593206e-08</v>
       </c>
       <c r="F12" t="n">
-        <v>9.264601585901033e-11</v>
+        <v>7.20502839612891e-08</v>
       </c>
       <c r="G12" t="n">
-        <v>3.959498701133768e-11</v>
+        <v>2.172687274537566e-08</v>
       </c>
       <c r="H12" t="n">
-        <v>6.856931689114276e-11</v>
+        <v>3.561792993878043e-08</v>
       </c>
       <c r="I12" t="n">
-        <v>4.582202672853697e-13</v>
+        <v>2.015026545620913e-08</v>
       </c>
       <c r="J12" t="n">
-        <v>2.26672444703091e-10</v>
+        <v>1.337520849631346e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>9.941601014640256e-11</v>
+        <v>2.106646519450805e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>4.969029701595851e-11</v>
+        <v>6.806320129726373e-08</v>
       </c>
       <c r="M12" t="n">
-        <v>3.465780995526302e-10</v>
+        <v>8.257697459157498e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>8.61288956821582e-11</v>
+        <v>8.525071848453081e-08</v>
       </c>
       <c r="O12" t="n">
-        <v>3.575171270142619e-10</v>
+        <v>7.083897912707471e-08</v>
       </c>
       <c r="P12" t="n">
-        <v>1.300781010682428e-10</v>
+        <v>3.204424725566923e-09</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.119989266942014e-10</v>
+        <v>1.148199579859011e-08</v>
       </c>
       <c r="R12" t="n">
-        <v>4.485330856729419e-11</v>
+        <v>3.831539885368329e-08</v>
       </c>
       <c r="S12" t="n">
-        <v>2.432536810870189e-12</v>
+        <v>4.40344205543397e-09</v>
       </c>
       <c r="T12" t="n">
-        <v>8.064366015247959e-12</v>
+        <v>9.544326218247079e-09</v>
       </c>
       <c r="U12" t="n">
-        <v>9.247821952662605e-11</v>
+        <v>2.888740979756221e-08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.820638258209772e-11</v>
+        <v>2.362185558268948e-09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.971986463011888e-10</v>
+        <v>1.167151708614256e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>9.605571546500435e-12</v>
+        <v>2.209086424898032e-08</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.305227758154672e-10</v>
+        <v>4.193006830632839e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.353649716408285e-11</v>
+        <v>2.468943627320641e-08</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68597330540976e-10</v>
+        <v>2.537809962177562e-08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.112964650995529e-10</v>
+        <v>1.105840974346961e-09</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.42390099711065e-10</v>
+        <v>2.904718954255259e-08</v>
       </c>
       <c r="AD12" t="n">
-        <v>7.319328476640408e-11</v>
+        <v>1.530285942408227e-08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.426788825975578e-10</v>
+        <v>5.047839835015111e-08</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.59612650558239e-11</v>
+        <v>3.842125195774315e-08</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.546865496277917e-10</v>
+        <v>7.251054512380506e-08</v>
       </c>
       <c r="AH12" t="n">
-        <v>6.504620453373633e-11</v>
+        <v>9.588962512907528e-09</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.60374449831302e-10</v>
+        <v>4.875820280858534e-08</v>
       </c>
       <c r="AJ12" t="n">
-        <v>7.609776003780766e-11</v>
+        <v>6.666760921092418e-09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.036895131729555e-11</v>
+        <v>5.882845321991681e-09</v>
       </c>
       <c r="AL12" t="n">
-        <v>9.670891865098952e-11</v>
+        <v>4.851320412058158e-08</v>
       </c>
       <c r="AM12" t="n">
-        <v>9.015972690651353e-11</v>
+        <v>3.876990817275328e-08</v>
       </c>
       <c r="AN12" t="n">
-        <v>5.064574107316311e-11</v>
+        <v>2.593019310381806e-08</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.820925216167169e-10</v>
+        <v>2.036366986146732e-08</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.271074356878898e-10</v>
+        <v>2.159822187763893e-08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.464720011945531e-10</v>
+        <v>2.270121157721405e-08</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.024473561539452e-10</v>
+        <v>1.770019464331085e-09</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01378294647958e-10</v>
+        <v>1.448625885913657e-09</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.173946324825266e-13</v>
+        <v>3.190713693257408e-09</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.957686262046067e-11</v>
+        <v>1.448941588932939e-07</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.119806050808307e-11</v>
+        <v>4.84555009450105e-08</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.299079425784669e-10</v>
+        <v>1.348278111379386e-08</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.099913629764586e-11</v>
+        <v>9.971542169751046e-08</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.1664432161066e-12</v>
+        <v>8.690599884175754e-08</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.133554222709776e-10</v>
+        <v>3.263260772712329e-10</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.409204334450024e-11</v>
+        <v>1.443444830329099e-08</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.572462798333675e-10</v>
+        <v>2.860193859532956e-09</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.665989013410751e-10</v>
+        <v>1.596921173074861e-08</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.335534957242373e-11</v>
+        <v>2.976655189002031e-08</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.366138535103701e-11</v>
+        <v>3.312721830184273e-08</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.61026235348627e-11</v>
+        <v>2.106280927449689e-09</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.358779061488846e-11</v>
+        <v>6.069434732580703e-08</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.376813759170538e-11</v>
+        <v>5.118243162627323e-09</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.151407954038454e-11</v>
+        <v>1.02125667922337e-08</v>
       </c>
       <c r="BJ12" t="n">
-        <v>4.187980517933454e-10</v>
+        <v>4.399866782023309e-08</v>
       </c>
       <c r="BK12" t="n">
-        <v>3.677868426477104e-11</v>
+        <v>1.24328050077338e-08</v>
       </c>
       <c r="BL12" t="n">
-        <v>5.712349343545142e-11</v>
+        <v>4.613963655586417e-10</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.643597643187562e-11</v>
+        <v>1.568460916701042e-09</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.630165778036655e-11</v>
+        <v>1.660881565612726e-08</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.076800523747146e-10</v>
+        <v>8.675842266825384e-09</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.466460008980874e-10</v>
+        <v>4.082808402472438e-08</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.451874453994861e-10</v>
+        <v>7.049849592988267e-10</v>
       </c>
       <c r="BR12" t="n">
-        <v>3.363594472394205e-11</v>
+        <v>1.61451865210438e-08</v>
       </c>
       <c r="BS12" t="n">
-        <v>2.533312969121848e-12</v>
+        <v>2.095801043822121e-08</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.881610393692171e-11</v>
+        <v>4.152409527335976e-09</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.346413605607388e-11</v>
+        <v>1.201606991685367e-08</v>
       </c>
       <c r="BV12" t="n">
-        <v>2.194050843784545e-11</v>
+        <v>9.214208773755672e-08</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.381412601837329e-11</v>
+        <v>3.758761835115365e-08</v>
       </c>
       <c r="BX12" t="n">
-        <v>1.315093450804383e-10</v>
+        <v>1.026995288810895e-08</v>
       </c>
       <c r="BY12" t="n">
-        <v>6.872397095847305e-11</v>
+        <v>1.481607503350801e-09</v>
       </c>
       <c r="BZ12" t="n">
-        <v>9.550171764516335e-11</v>
+        <v>4.46841887935534e-08</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.863982440619694e-10</v>
+        <v>3.864353459448466e-08</v>
       </c>
       <c r="CB12" t="n">
-        <v>7.563203535676521e-11</v>
+        <v>9.308571691235557e-09</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.861400616975928e-10</v>
+        <v>2.460427239725504e-08</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.398210962097693e-11</v>
+        <v>6.094044713300661e-10</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.865713833426597e-11</v>
+        <v>6.769749916202272e-08</v>
       </c>
       <c r="CF12" t="n">
-        <v>9.807540890527378e-11</v>
+        <v>1.751041089903538e-09</v>
       </c>
       <c r="CG12" t="n">
-        <v>9.248374288617356e-11</v>
+        <v>1.432751695062962e-08</v>
       </c>
       <c r="CH12" t="n">
-        <v>6.404383967595351e-11</v>
+        <v>1.775431179851239e-08</v>
       </c>
       <c r="CI12" t="n">
-        <v>3.070989990083817e-11</v>
+        <v>2.253778497163239e-08</v>
       </c>
       <c r="CJ12" t="n">
-        <v>3.491645861330994e-11</v>
+        <v>8.275637064514285e-09</v>
       </c>
       <c r="CK12" t="n">
-        <v>3.791282912612992e-11</v>
+        <v>5.421315396603177e-09</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.278323280562432e-10</v>
+        <v>3.169517093226659e-09</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.171112790077089e-10</v>
+        <v>5.417994231038392e-08</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.160457091004986e-10</v>
+        <v>1.043105868347993e-07</v>
       </c>
       <c r="CO12" t="n">
-        <v>5.466831154432583e-11</v>
+        <v>7.545952485088492e-08</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.451454039764656e-10</v>
+        <v>1.351048517506115e-08</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1.116957290547838e-10</v>
+        <v>2.220784445228219e-08</v>
       </c>
       <c r="CR12" t="n">
-        <v>2.08795827849606e-10</v>
+        <v>3.673350335020586e-08</v>
       </c>
       <c r="CS12" t="n">
-        <v>1.197369703387352e-10</v>
+        <v>3.524222336181992e-08</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.1824493040844e-10</v>
+        <v>1.214260914039755e-10</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.776742988846003e-11</v>
+        <v>4.201466730080483e-09</v>
       </c>
       <c r="CV12" t="n">
-        <v>4.426433525273055e-11</v>
+        <v>1.501671675896432e-09</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.113383079649367e-11</v>
+        <v>6.245246453318032e-08</v>
       </c>
       <c r="CX12" t="n">
-        <v>3.739584336637236e-11</v>
+        <v>8.465671719193324e-09</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.639642033257616e-10</v>
+        <v>1.960662743272223e-08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>6.435535437887552e-11</v>
+        <v>2.649335684168364e-08</v>
       </c>
       <c r="DA12" t="n">
-        <v>5.556093779501836e-11</v>
+        <v>2.225720052706492e-08</v>
       </c>
       <c r="DB12" t="n">
-        <v>4.083711840907611e-11</v>
+        <v>1.243870428879745e-08</v>
       </c>
       <c r="DC12" t="n">
-        <v>4.298119152257307e-11</v>
+        <v>6.576086342136023e-09</v>
       </c>
       <c r="DD12" t="n">
-        <v>8.921552385743325e-11</v>
+        <v>1.068097255085831e-08</v>
       </c>
       <c r="DE12" t="n">
-        <v>3.273599447073394e-11</v>
+        <v>1.690378859109387e-08</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.128695136827119e-10</v>
+        <v>1.234275615047409e-08</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.959077037902659e-10</v>
+        <v>5.248516288247629e-09</v>
       </c>
       <c r="DH12" t="n">
-        <v>7.880975871898954e-10</v>
+        <v>1.778526481643894e-08</v>
       </c>
       <c r="DI12" t="n">
-        <v>3.227058620325352e-10</v>
+        <v>5.665591551462512e-09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>6.013239906010881e-11</v>
+        <v>8.916894955746102e-08</v>
       </c>
       <c r="DK12" t="n">
-        <v>1.283573768107171e-11</v>
+        <v>8.840699727841184e-09</v>
       </c>
       <c r="DL12" t="n">
-        <v>5.236794886620544e-10</v>
+        <v>5.99982215021555e-08</v>
       </c>
       <c r="DM12" t="n">
-        <v>1.546749534009351e-11</v>
+        <v>1.466916099701621e-08</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.649347151910785e-11</v>
+        <v>1.419440920358284e-08</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.694944705421531e-11</v>
+        <v>3.898234623989083e-08</v>
       </c>
       <c r="DP12" t="n">
-        <v>1.325150544850828e-10</v>
+        <v>4.813226262001535e-09</v>
       </c>
       <c r="DQ12" t="n">
-        <v>5.653350704237781e-11</v>
+        <v>1.525466686302934e-08</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.757732816195741e-11</v>
+        <v>1.030536722623765e-08</v>
       </c>
       <c r="DS12" t="n">
-        <v>1.601885984969798e-10</v>
+        <v>9.005757917179835e-09</v>
       </c>
       <c r="DT12" t="n">
-        <v>2.201721617522967e-11</v>
+        <v>3.349655841589083e-08</v>
       </c>
       <c r="DU12" t="n">
-        <v>5.369863234627736e-11</v>
+        <v>7.242642041660474e-09</v>
       </c>
       <c r="DV12" t="n">
-        <v>2.889709860287581e-10</v>
+        <v>2.404612331474709e-08</v>
       </c>
       <c r="DW12" t="n">
-        <v>1.250624187543181e-10</v>
+        <v>6.264030960601019e-10</v>
       </c>
       <c r="DX12" t="n">
-        <v>1.393549685368978e-11</v>
+        <v>2.83536216727498e-08</v>
       </c>
       <c r="DY12" t="n">
-        <v>2.139269872358796e-10</v>
+        <v>2.615612970657821e-08</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.649715334981153e-11</v>
+        <v>3.129690950842701e-09</v>
       </c>
       <c r="EA12" t="n">
-        <v>1.094169893578467e-10</v>
+        <v>4.8882640157899e-08</v>
       </c>
       <c r="EB12" t="n">
-        <v>2.715712932310765e-10</v>
+        <v>4.30305462373326e-08</v>
       </c>
       <c r="EC12" t="n">
-        <v>6.786630979416231e-11</v>
+        <v>2.35127961545345e-09</v>
       </c>
       <c r="ED12" t="n">
-        <v>5.570290409484535e-11</v>
+        <v>5.503622801938945e-08</v>
       </c>
       <c r="EE12" t="n">
-        <v>1.726142319358193e-11</v>
+        <v>6.810640229559795e-08</v>
       </c>
       <c r="EF12" t="n">
-        <v>2.626534753580323e-11</v>
+        <v>2.668138154859889e-09</v>
       </c>
       <c r="EG12" t="n">
-        <v>2.366974498346774e-11</v>
+        <v>2.405411692052439e-08</v>
       </c>
       <c r="EH12" t="n">
-        <v>6.084661247074408e-11</v>
+        <v>3.010124061120223e-08</v>
       </c>
       <c r="EI12" t="n">
-        <v>7.852890560045012e-11</v>
+        <v>1.484098088866403e-08</v>
       </c>
       <c r="EJ12" t="n">
-        <v>4.339915926632187e-11</v>
+        <v>2.18818403396881e-08</v>
       </c>
       <c r="EK12" t="n">
-        <v>4.923690968827721e-11</v>
+        <v>2.103549867626953e-08</v>
       </c>
       <c r="EL12" t="n">
-        <v>6.414248993058536e-11</v>
+        <v>1.690782092111931e-08</v>
       </c>
       <c r="EM12" t="n">
-        <v>1.276027807722846e-11</v>
+        <v>6.926643258964305e-09</v>
       </c>
       <c r="EN12" t="n">
-        <v>7.8795442393087e-11</v>
+        <v>2.068067672666984e-08</v>
       </c>
       <c r="EO12" t="n">
-        <v>3.929590680629147e-11</v>
+        <v>7.987992489688622e-09</v>
       </c>
       <c r="EP12" t="n">
-        <v>1.306781072241137e-10</v>
+        <v>5.267354907800836e-08</v>
       </c>
       <c r="EQ12" t="n">
-        <v>9.110329157735464e-11</v>
+        <v>1.393481241507288e-08</v>
       </c>
       <c r="ER12" t="n">
-        <v>2.866486562003168e-11</v>
+        <v>8.86313245018755e-12</v>
       </c>
       <c r="ES12" t="n">
-        <v>2.659047149133897e-10</v>
+        <v>1.518261782962327e-08</v>
       </c>
       <c r="ET12" t="n">
-        <v>1.051480430502849e-10</v>
+        <v>1.14903766501584e-08</v>
       </c>
       <c r="EU12" t="n">
-        <v>3.271150711414705e-11</v>
+        <v>3.600298725814355e-09</v>
       </c>
       <c r="EV12" t="n">
-        <v>2.512785535202511e-10</v>
+        <v>7.251239608763171e-09</v>
       </c>
       <c r="EW12" t="n">
-        <v>8.587446032048973e-11</v>
+        <v>2.590108039157712e-08</v>
       </c>
       <c r="EX12" t="n">
-        <v>5.159475624516574e-11</v>
+        <v>5.695173777020557e-10</v>
       </c>
       <c r="EY12" t="n">
-        <v>8.061976433659801e-12</v>
+        <v>6.955012565867946e-08</v>
       </c>
       <c r="EZ12" t="n">
-        <v>6.989597095552469e-11</v>
+        <v>6.738251734361711e-09</v>
       </c>
       <c r="FA12" t="n">
-        <v>1.21648247031203e-10</v>
+        <v>1.787486603177513e-08</v>
       </c>
       <c r="FB12" t="n">
-        <v>4.552332122376157e-11</v>
+        <v>1.382921599457632e-08</v>
       </c>
       <c r="FC12" t="n">
-        <v>3.442663515373923e-11</v>
+        <v>2.068257565213116e-08</v>
       </c>
       <c r="FD12" t="n">
-        <v>4.730331057412052e-11</v>
+        <v>7.491091080780166e-11</v>
       </c>
       <c r="FE12" t="n">
-        <v>2.377358553073972e-11</v>
+        <v>5.394458213459075e-09</v>
       </c>
       <c r="FF12" t="n">
-        <v>1.198158100512714e-10</v>
+        <v>1.819633155264455e-08</v>
       </c>
       <c r="FG12" t="n">
-        <v>6.080588116352814e-11</v>
+        <v>1.458507803420162e-08</v>
       </c>
       <c r="FH12" t="n">
-        <v>1.181131303873428e-10</v>
+        <v>1.735809540548416e-08</v>
       </c>
       <c r="FI12" t="n">
-        <v>2.288662592775381e-10</v>
+        <v>2.705626833687802e-09</v>
       </c>
       <c r="FJ12" t="n">
-        <v>2.022118444910959e-10</v>
+        <v>1.799228854793e-08</v>
       </c>
       <c r="FK12" t="n">
-        <v>1.366796814616933e-10</v>
+        <v>6.602558055845975e-09</v>
       </c>
       <c r="FL12" t="n">
-        <v>2.919416791646867e-11</v>
+        <v>2.081380223728502e-08</v>
       </c>
       <c r="FM12" t="n">
-        <v>1.522046655377807e-10</v>
+        <v>1.604389687770436e-08</v>
       </c>
       <c r="FN12" t="n">
-        <v>1.17612697358993e-10</v>
+        <v>2.151749001200187e-08</v>
       </c>
       <c r="FO12" t="n">
-        <v>3.491849864811769e-11</v>
+        <v>4.195007363705372e-08</v>
       </c>
       <c r="FP12" t="n">
-        <v>6.487600734406129e-11</v>
+        <v>3.453143193610231e-08</v>
       </c>
       <c r="FQ12" t="n">
-        <v>1.629115245482815e-12</v>
+        <v>6.666926566367692e-08</v>
       </c>
       <c r="FR12" t="n">
-        <v>3.190250841278441e-11</v>
+        <v>3.338444543032892e-08</v>
       </c>
       <c r="FS12" t="n">
-        <v>3.797259034987732e-11</v>
+        <v>2.24986607122446e-08</v>
       </c>
       <c r="FT12" t="n">
-        <v>1.124582232892024e-10</v>
+        <v>6.61129888612777e-08</v>
       </c>
       <c r="FU12" t="n">
-        <v>5.383082174459375e-11</v>
+        <v>2.758624439991308e-08</v>
       </c>
       <c r="FV12" t="n">
-        <v>2.614599509120907e-11</v>
+        <v>3.321217079133021e-08</v>
       </c>
       <c r="FW12" t="n">
-        <v>6.428007431891203e-12</v>
+        <v>2.774346796741156e-08</v>
       </c>
       <c r="FX12" t="n">
-        <v>4.569988051178475e-12</v>
+        <v>1.660902171352063e-08</v>
       </c>
       <c r="FY12" t="n">
-        <v>1.489395967668727e-10</v>
+        <v>1.686064510231233e-09</v>
       </c>
       <c r="FZ12" t="n">
-        <v>1.402003235728699e-10</v>
+        <v>1.459563669925501e-08</v>
       </c>
       <c r="GA12" t="n">
-        <v>5.938000091632034e-11</v>
+        <v>1.121332360298766e-08</v>
       </c>
       <c r="GB12" t="n">
-        <v>6.468682794275038e-12</v>
+        <v>2.373863061677639e-08</v>
       </c>
       <c r="GC12" t="n">
-        <v>1.305323765743438e-10</v>
+        <v>1.902880519821792e-09</v>
       </c>
       <c r="GD12" t="n">
-        <v>3.780142865394964e-11</v>
+        <v>4.284326138304095e-08</v>
       </c>
       <c r="GE12" t="n">
-        <v>3.444475260572233e-10</v>
+        <v>5.016393345158576e-08</v>
       </c>
       <c r="GF12" t="n">
-        <v>1.481323119723044e-10</v>
+        <v>5.385138557301161e-09</v>
       </c>
       <c r="GG12" t="n">
-        <v>2.113133418246704e-10</v>
+        <v>3.111205515438087e-08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0002604331530164927</v>
+        <v>0.0007177041843533516</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001660062931478024</v>
+        <v>0.02713383734226227</v>
       </c>
       <c r="C13" t="n">
-        <v>6.651979492744431e-05</v>
+        <v>0.01757293753325939</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0008850174490362406</v>
+        <v>0.01173534151166677</v>
       </c>
       <c r="E13" t="n">
-        <v>6.145401857793331e-05</v>
+        <v>0.01645819284021854</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001480439677834511</v>
+        <v>0.03250168636441231</v>
       </c>
       <c r="G13" t="n">
-        <v>5.837149365106598e-05</v>
+        <v>0.005419558379799128</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0002766400284599513</v>
+        <v>0.02274600975215435</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0001205522348755039</v>
+        <v>0.002489428734406829</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0003750566975213587</v>
+        <v>0.002255279570817947</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001378772314637899</v>
+        <v>0.06503370404243469</v>
       </c>
       <c r="L13" t="n">
-        <v>6.708537694066763e-05</v>
+        <v>0.0131165087223053</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0009362052660435438</v>
+        <v>0.00863195862621069</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0001405906659783795</v>
+        <v>0.03045442886650562</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00148351676762104</v>
+        <v>0.04305170103907585</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0001717457344057038</v>
+        <v>0.0200317744165659</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.726692426018417e-05</v>
+        <v>0.001047845697030425</v>
       </c>
       <c r="R13" t="n">
-        <v>9.732496982906014e-05</v>
+        <v>0.00915799755603075</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001025252640829422</v>
+        <v>0.008339914493262768</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0002459709940012544</v>
+        <v>0.0006416793912649155</v>
       </c>
       <c r="U13" t="n">
-        <v>2.064443833660334e-07</v>
+        <v>0.002186814555898309</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0002349505957681686</v>
+        <v>0.01271499134600163</v>
       </c>
       <c r="W13" t="n">
-        <v>6.716658390359953e-05</v>
+        <v>0.01379647850990295</v>
       </c>
       <c r="X13" t="n">
-        <v>2.123889134963974e-05</v>
+        <v>0.009028872475028038</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0001111570600187406</v>
+        <v>0.007087830919772387</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.440048648277298e-06</v>
+        <v>0.02497799508273602</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0001796883443603292</v>
+        <v>0.00661475770175457</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.715649993158877e-05</v>
+        <v>0.0208719577640295</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0001541853416711092</v>
+        <v>0.002446669153869152</v>
       </c>
       <c r="AD13" t="n">
-        <v>7.547512359451503e-05</v>
+        <v>0.008146744221448898</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0001584462297614664</v>
+        <v>0.001115363440476358</v>
       </c>
       <c r="AF13" t="n">
-        <v>4.400765465106815e-05</v>
+        <v>0.03239766135811806</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.171446173335426e-05</v>
+        <v>0.0036106260959059</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0002922421554103494</v>
+        <v>0.01295360177755356</v>
       </c>
       <c r="AI13" t="n">
-        <v>9.738860535435379e-05</v>
+        <v>0.02688544429838657</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7.241370622068644e-05</v>
+        <v>0.003276215167716146</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0001746597117744386</v>
+        <v>0.00580526189878583</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0002494444197509438</v>
+        <v>0.002889998955652118</v>
       </c>
       <c r="AM13" t="n">
-        <v>8.002412505447865e-05</v>
+        <v>0.005345340352505445</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.546274380525574e-05</v>
+        <v>0.00501971784979105</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.613904350961093e-05</v>
+        <v>0.009801280684769154</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.000245173490839079</v>
+        <v>0.002380973659455776</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0001286412007175386</v>
+        <v>0.006610042415559292</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.950253499671817e-05</v>
+        <v>0.02058379538357258</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0001606988080311567</v>
+        <v>0.003223673207685351</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0002528015756979585</v>
+        <v>0.003280889475718141</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.001266594743356109</v>
+        <v>0.05873343348503113</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0001425498339813203</v>
+        <v>0.00959528423845768</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0001566908613312989</v>
+        <v>0.008456985466182232</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0003451613301876932</v>
+        <v>0.01884024776518345</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0007440198678523302</v>
+        <v>0.03687097877264023</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0001451189164072275</v>
+        <v>0.003138713072985411</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0002617205027490854</v>
+        <v>0.006107279099524021</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0002012876211665571</v>
+        <v>0.00515297707170248</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0001927924167830497</v>
+        <v>0.01183657441288233</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0003194980672560632</v>
+        <v>0.006452912464737892</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0003961033944506198</v>
+        <v>0.002173872664570808</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.000448762031737715</v>
+        <v>0.007598418742418289</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0005152715020813048</v>
+        <v>0.008220684714615345</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0005708853132091463</v>
+        <v>0.00702309887856245</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.655704884091392e-05</v>
+        <v>0.007765139453113079</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0003353726642671973</v>
+        <v>0.02392943948507309</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.480764593812637e-05</v>
+        <v>0.008538380265235901</v>
       </c>
       <c r="BL13" t="n">
-        <v>8.866811549523845e-05</v>
+        <v>0.008077230304479599</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0004013545403722674</v>
+        <v>0.02517247013747692</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0001040540300891735</v>
+        <v>0.00319651747122407</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0003669765428639948</v>
+        <v>0.0125140342861414</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0003132672281935811</v>
+        <v>0.01677883788943291</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.107226338121109e-06</v>
+        <v>0.0001273037341888994</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0002570191281847656</v>
+        <v>0.002904258668422699</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.029626042116433e-05</v>
+        <v>0.01543673500418663</v>
       </c>
       <c r="BT13" t="n">
-        <v>3.414385719224811e-05</v>
+        <v>0.001676761079579592</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0001216333475895226</v>
+        <v>0.003391305450350046</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.0006203593802638352</v>
+        <v>0.03019963204860687</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.085572876036167e-08</v>
+        <v>0.003548307809978724</v>
       </c>
       <c r="BX13" t="n">
-        <v>4.784129487234168e-05</v>
+        <v>0.01576042547821999</v>
       </c>
       <c r="BY13" t="n">
-        <v>3.939406815334223e-05</v>
+        <v>0.01128065958619118</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0001333430700469762</v>
+        <v>0.01437634229660034</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0002342527877772227</v>
+        <v>0.004712292458862066</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0001548231521155685</v>
+        <v>0.01287583261728287</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0001627870806260034</v>
+        <v>0.002085806801915169</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.934180858777836e-05</v>
+        <v>0.009131354279816151</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0003175743040628731</v>
+        <v>0.01024176646023989</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0001295849069720134</v>
+        <v>0.006589442025870085</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0001821978075895458</v>
+        <v>0.0004583165573421866</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0001147993971244432</v>
+        <v>0.007714952807873487</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0002603350149001926</v>
+        <v>0.01295460481196642</v>
       </c>
       <c r="CJ13" t="n">
-        <v>6.783636490581557e-05</v>
+        <v>0.004258214496076107</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.856555172707886e-05</v>
+        <v>0.002559380838647485</v>
       </c>
       <c r="CL13" t="n">
-        <v>9.81505581876263e-05</v>
+        <v>0.002029038034379482</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0002454123459756374</v>
+        <v>0.002586400136351585</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0002099352423101664</v>
+        <v>0.03698763623833656</v>
       </c>
       <c r="CO13" t="n">
-        <v>4.348433139966801e-05</v>
+        <v>0.004089318215847015</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0002421570825390518</v>
+        <v>0.02304987236857414</v>
       </c>
       <c r="CQ13" t="n">
-        <v>8.676296420162544e-05</v>
+        <v>0.01148730516433716</v>
       </c>
       <c r="CR13" t="n">
-        <v>2.678458258742467e-05</v>
+        <v>0.01441608741879463</v>
       </c>
       <c r="CS13" t="n">
-        <v>4.322004315326922e-05</v>
+        <v>0.01014673430472612</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0002076459059026092</v>
+        <v>0.0002899126848205924</v>
       </c>
       <c r="CU13" t="n">
-        <v>5.697711094398983e-05</v>
+        <v>0.002826898824423552</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.945233998412732e-05</v>
+        <v>0.007095723412930965</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0002406459971098229</v>
+        <v>0.008721835911273956</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0001061745133483782</v>
+        <v>0.005147452931851149</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0002581325243227184</v>
+        <v>0.002767119323834777</v>
       </c>
       <c r="CZ13" t="n">
-        <v>7.903379446361214e-05</v>
+        <v>0.004132093861699104</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0002423120167804882</v>
+        <v>0.01295475475490093</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0001081159207387827</v>
+        <v>0.0007477838662452996</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0001418528845533729</v>
+        <v>0.004063940141350031</v>
       </c>
       <c r="DD13" t="n">
-        <v>5.19130117027089e-05</v>
+        <v>0.004289665725082159</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.000135701586259529</v>
+        <v>0.01081765536218882</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0005586037295870483</v>
+        <v>0.007710089907050133</v>
       </c>
       <c r="DG13" t="n">
-        <v>4.514932152233087e-05</v>
+        <v>0.02082560025155544</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0004104810650460422</v>
+        <v>0.01739304885268211</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0001044502932927571</v>
+        <v>0.02171801589429379</v>
       </c>
       <c r="DJ13" t="n">
-        <v>5.613958273897879e-05</v>
+        <v>0.002032240852713585</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0003330562612973154</v>
+        <v>0.01566982083022594</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0003080603200942278</v>
+        <v>0.002840653294697404</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.000207724588108249</v>
+        <v>0.002193099353462458</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0001522573438705876</v>
+        <v>0.008900490589439869</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0001600317191332579</v>
+        <v>0.01519665494561195</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0001915666653076187</v>
+        <v>0.001154945697635412</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0003154341829940677</v>
+        <v>0.01317218504846096</v>
       </c>
       <c r="DR13" t="n">
-        <v>5.005897037335671e-05</v>
+        <v>0.01686766743659973</v>
       </c>
       <c r="DS13" t="n">
-        <v>2.507666795281693e-05</v>
+        <v>0.002944610081613064</v>
       </c>
       <c r="DT13" t="n">
-        <v>1.790030000847764e-05</v>
+        <v>0.003752220189198852</v>
       </c>
       <c r="DU13" t="n">
-        <v>3.611654392443597e-05</v>
+        <v>0.02844442427158356</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0001334886765107512</v>
+        <v>0.00287189893424511</v>
       </c>
       <c r="DW13" t="n">
-        <v>2.088624387397431e-05</v>
+        <v>0.01303072366863489</v>
       </c>
       <c r="DX13" t="n">
-        <v>1.888238875835668e-05</v>
+        <v>0.007367003709077835</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0001305212790612131</v>
+        <v>0.008971930481493473</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.946182939922437e-05</v>
+        <v>0.003400762099772692</v>
       </c>
       <c r="EA13" t="n">
-        <v>5.527559915208258e-05</v>
+        <v>0.001050564227625728</v>
       </c>
       <c r="EB13" t="n">
-        <v>7.33380948076956e-05</v>
+        <v>0.01639197766780853</v>
       </c>
       <c r="EC13" t="n">
-        <v>5.737891115131788e-06</v>
+        <v>0.002451960230246186</v>
       </c>
       <c r="ED13" t="n">
-        <v>3.156361344736069e-05</v>
+        <v>0.007414503488689661</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0001139950400101952</v>
+        <v>0.0118528213351965</v>
       </c>
       <c r="EF13" t="n">
-        <v>8.087965397862718e-05</v>
+        <v>0.006337425205856562</v>
       </c>
       <c r="EG13" t="n">
-        <v>9.315184433944523e-05</v>
+        <v>0.005950721446424723</v>
       </c>
       <c r="EH13" t="n">
-        <v>2.390327063039877e-05</v>
+        <v>0.005864216014742851</v>
       </c>
       <c r="EI13" t="n">
-        <v>6.582539208466187e-05</v>
+        <v>0.009056712500751019</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0001037644542520866</v>
+        <v>0.004434596281498671</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0001915564062073827</v>
+        <v>0.01366602256894112</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0001423837529728189</v>
+        <v>0.002333737211301923</v>
       </c>
       <c r="EM13" t="n">
-        <v>4.259170236764476e-05</v>
+        <v>0.007339415140450001</v>
       </c>
       <c r="EN13" t="n">
-        <v>7.497717888327315e-05</v>
+        <v>0.004089240450412035</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0001492214214522392</v>
+        <v>0.004087207373231649</v>
       </c>
       <c r="EP13" t="n">
-        <v>9.907320782076567e-05</v>
+        <v>0.0008891699835658073</v>
       </c>
       <c r="EQ13" t="n">
-        <v>4.889783303951845e-05</v>
+        <v>0.004202554933726788</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0001094239487429149</v>
+        <v>0.01003076229244471</v>
       </c>
       <c r="ES13" t="n">
-        <v>4.580825043376535e-05</v>
+        <v>0.003785496111959219</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0003501644532661885</v>
+        <v>0.004275294952094555</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0001140184176620096</v>
+        <v>0.00640028016641736</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0001892761356430128</v>
+        <v>0.0009394584922119975</v>
       </c>
       <c r="EW13" t="n">
-        <v>1.982333196792752e-05</v>
+        <v>0.00583572406321764</v>
       </c>
       <c r="EX13" t="n">
-        <v>2.787281846394762e-05</v>
+        <v>0.008875073865056038</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0002219843299826607</v>
+        <v>0.01158079598098993</v>
       </c>
       <c r="EZ13" t="n">
-        <v>5.45491129742004e-05</v>
+        <v>0.005790494382381439</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0001736406702548265</v>
+        <v>1.920807699207217e-05</v>
       </c>
       <c r="FB13" t="n">
-        <v>8.751214772928506e-05</v>
+        <v>0.003856662660837173</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0002405312698101625</v>
+        <v>0.01369359437376261</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0001185969813377596</v>
+        <v>0.005700338631868362</v>
       </c>
       <c r="FE13" t="n">
-        <v>1.919395072036423e-05</v>
+        <v>0.0002304065710632131</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0001269115164177492</v>
+        <v>0.004565093666315079</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0001003931538434699</v>
+        <v>0.008477297611534595</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0001715344260446727</v>
+        <v>0.001405069138854742</v>
       </c>
       <c r="FI13" t="n">
-        <v>6.542187475133687e-05</v>
+        <v>0.0006719091907143593</v>
       </c>
       <c r="FJ13" t="n">
-        <v>6.901176675455645e-05</v>
+        <v>0.01261657662689686</v>
       </c>
       <c r="FK13" t="n">
-        <v>2.874253914342262e-05</v>
+        <v>0.00397211592644453</v>
       </c>
       <c r="FL13" t="n">
-        <v>8.015885396162048e-05</v>
+        <v>0.004241751972585917</v>
       </c>
       <c r="FM13" t="n">
-        <v>1.71800893440377e-05</v>
+        <v>0.01056274864822626</v>
       </c>
       <c r="FN13" t="n">
-        <v>3.40883489116095e-05</v>
+        <v>0.01926427893340588</v>
       </c>
       <c r="FO13" t="n">
-        <v>4.496003020904027e-05</v>
+        <v>0.004071108531206846</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.000184750446351245</v>
+        <v>0.007323115132749081</v>
       </c>
       <c r="FQ13" t="n">
-        <v>4.34481116826646e-05</v>
+        <v>0.01574864611029625</v>
       </c>
       <c r="FR13" t="n">
-        <v>6.864908300485695e-06</v>
+        <v>0.01521262340247631</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0001602564589120448</v>
+        <v>0.01096479594707489</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0007266367319971323</v>
+        <v>0.008020889945328236</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0001876603928394616</v>
+        <v>0.0119487326592207</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0001022360156639479</v>
+        <v>0.0131121464073658</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0002137887058779597</v>
+        <v>0.006940804421901703</v>
       </c>
       <c r="FX13" t="n">
-        <v>1.783423067536205e-05</v>
+        <v>0.009361072443425655</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.000176468282006681</v>
+        <v>0.006102483719587326</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0001986189890885726</v>
+        <v>0.01046179048717022</v>
       </c>
       <c r="GA13" t="n">
-        <v>2.638451042002998e-05</v>
+        <v>0.001381405163556337</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0002201545430580154</v>
+        <v>0.008845868520438671</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.000119418793474324</v>
+        <v>0.007943139411509037</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0001607225422048941</v>
+        <v>0.00234927493147552</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0004817972076125443</v>
+        <v>0.001530423993244767</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0002362199884373695</v>
+        <v>0.007184091955423355</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0001478980702813715</v>
+        <v>0.01577983982861042</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.001940644928254187</v>
+        <v>1.099130440707086e-05</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0007836328586563468</v>
+        <v>5.720159970223904e-05</v>
       </c>
       <c r="C14" t="n">
-        <v>0.005424166098237038</v>
+        <v>0.0001324637414654717</v>
       </c>
       <c r="D14" t="n">
-        <v>0.004241309594362974</v>
+        <v>0.0001387688389513642</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003430936019867659</v>
+        <v>2.791815131786279e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001347145065665245</v>
+        <v>6.372737698256969e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001512803602963686</v>
+        <v>2.403101098025218e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0004483723314478993</v>
+        <v>5.346528632799163e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00147357489913702</v>
+        <v>9.417269757250324e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001678086933679879</v>
+        <v>2.133668749593198e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0006897248676978052</v>
+        <v>5.689341196557507e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004336296580731869</v>
+        <v>0.0001695616665529087</v>
       </c>
       <c r="M14" t="n">
-        <v>0.004481583368033171</v>
+        <v>0.0001846233499236405</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0008620326989330351</v>
+        <v>2.882469925680198e-05</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001032154308632016</v>
+        <v>8.177090785466135e-05</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000973094895016402</v>
+        <v>1.540605808258988e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.907615508884192e-05</v>
+        <v>0.0001041938958223909</v>
       </c>
       <c r="R14" t="n">
-        <v>0.00223807105794549</v>
+        <v>4.839649045607075e-05</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0005754177691414952</v>
+        <v>1.519987199571915e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0009735169587656856</v>
+        <v>6.063885393814417e-07</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0009001068538054824</v>
+        <v>2.932640563813038e-05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0008529489277862012</v>
+        <v>2.448724262649193e-05</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0005921403062529862</v>
+        <v>2.68568310275441e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0003384758601896465</v>
+        <v>4.163610719842836e-05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0006150910048745573</v>
+        <v>1.871596759883687e-05</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.000615636061411351</v>
+        <v>7.964774340507574e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0001165692301583476</v>
+        <v>3.962816117564216e-05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.001733011798933148</v>
+        <v>2.344062886550091e-05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0004186437872704118</v>
+        <v>2.277366729686037e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0001725502515910193</v>
+        <v>9.794449397304561e-06</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.00169046560768038</v>
+        <v>7.010393164819106e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.001229697256349027</v>
+        <v>6.229547580005601e-06</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.100642738398165e-05</v>
+        <v>1.184870870929444e-05</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0001107537827920169</v>
+        <v>1.40674728754675e-05</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0007400678587146103</v>
+        <v>4.515060936682858e-05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0008735440205782652</v>
+        <v>2.742710603342857e-05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0005085358279757202</v>
+        <v>8.859172339725774e-06</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.867701161652803e-05</v>
+        <v>2.631024472066201e-06</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.867559669539332e-05</v>
+        <v>3.531724723870866e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0002893874188885093</v>
+        <v>2.712251807679422e-05</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.001079939771443605</v>
+        <v>5.002557372790761e-05</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.000205748830921948</v>
+        <v>1.03146394394571e-05</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0004582849214784801</v>
+        <v>2.461667281750124e-05</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0001277374685741961</v>
+        <v>2.438227602397092e-05</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0003384562442079186</v>
+        <v>4.099097714060917e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.001672412035986781</v>
+        <v>3.405331517569721e-05</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.00197251420468092</v>
+        <v>1.099890141631477e-05</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.002881304826587439</v>
+        <v>0.0001666581956669688</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.003587491344660521</v>
+        <v>0.0001172565171145834</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0007278397097252309</v>
+        <v>4.430571607372258e-06</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0008510386687703431</v>
+        <v>9.110024257097393e-05</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.001072114333510399</v>
+        <v>8.399052603635937e-05</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.001039177644997835</v>
+        <v>3.49062102031894e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0005490191979333758</v>
+        <v>7.620284304721281e-05</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.001466139918193221</v>
+        <v>3.924167685909197e-05</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.002806621138006449</v>
+        <v>1.905474891827907e-05</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0008888319716788828</v>
+        <v>2.491673876647837e-05</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.001535905874334276</v>
+        <v>2.267203672090545e-05</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.001382606336846948</v>
+        <v>1.348567002423806e-05</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.002156517235562205</v>
+        <v>4.339770384831354e-05</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.001204599859192967</v>
+        <v>6.738088268321007e-05</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0003912892425432801</v>
+        <v>5.854096889379434e-05</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.001732073491439223</v>
+        <v>4.983721373719163e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0001554047630634159</v>
+        <v>4.525789336184971e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0005930118495598435</v>
+        <v>4.597762745106593e-05</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.000785736832767725</v>
+        <v>4.614862064045155e-06</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.825109838042408e-05</v>
+        <v>3.007615305250511e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0006493370165117085</v>
+        <v>4.542525130091235e-05</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0002448419691063464</v>
+        <v>9.140408110397402e-06</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0001440444320905954</v>
+        <v>6.51135815132875e-06</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0007715169922448695</v>
+        <v>7.487426046282053e-05</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0003543170751072466</v>
+        <v>1.439306106476579e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0004338709404692054</v>
+        <v>9.487785064266063e-07</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.001227831817232072</v>
+        <v>2.74575904768426e-05</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.002005850663408637</v>
+        <v>9.847685578279197e-05</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.002415986265987158</v>
+        <v>0.0001122180983657017</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.001138628693297505</v>
+        <v>9.896532901620958e-06</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0003573236172087491</v>
+        <v>3.770732291741297e-05</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0003665828844532371</v>
+        <v>2.378767021582462e-05</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0007240429986268282</v>
+        <v>2.357462108193431e-05</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0008754605078138411</v>
+        <v>4.704228922491893e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0006133487331680954</v>
+        <v>3.083988303842489e-06</v>
       </c>
       <c r="CE14" t="n">
-        <v>4.437251482158899e-05</v>
+        <v>1.107646494347136e-05</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.001316740992479026</v>
+        <v>4.507420453592204e-05</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0007441614870913327</v>
+        <v>5.363755190046504e-05</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.000746953533962369</v>
+        <v>1.142978908319492e-05</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0002855350612662733</v>
+        <v>2.229360507044476e-05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0004948971327394247</v>
+        <v>4.327043825469445e-07</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0004280165303498507</v>
+        <v>7.715739229752216e-06</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0001784911000868306</v>
+        <v>1.168660583061865e-05</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.001911562983877957</v>
+        <v>5.964472620689776e-06</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.001580640207976103</v>
+        <v>9.476817467657384e-06</v>
       </c>
       <c r="CO14" t="n">
-        <v>2.92710610665381e-05</v>
+        <v>6.332717020995915e-05</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0008086480665951967</v>
+        <v>0.0001034233573591337</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0003918526053894311</v>
+        <v>5.630079613183625e-06</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0005399271030910313</v>
+        <v>4.877299579675309e-05</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.00044848961988464</v>
+        <v>9.532341209705919e-06</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.001906434074044228</v>
+        <v>1.301439806411508e-05</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0004118373326491565</v>
+        <v>3.457091224845499e-05</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0004684184968937188</v>
+        <v>6.332266366371186e-06</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0004318640858400613</v>
+        <v>2.570451033534482e-05</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0009292477043345571</v>
+        <v>3.771765841520391e-05</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0008315108134411275</v>
+        <v>4.768371945829131e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0004088668792974204</v>
+        <v>1.459755003452301e-05</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0001586735888849944</v>
+        <v>3.346794619574212e-05</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0004803854390047491</v>
+        <v>3.494254997349344e-06</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0003265505947638303</v>
+        <v>7.989102414285298e-06</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.0001124227856053039</v>
+        <v>1.322018670180114e-05</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0002241733891423792</v>
+        <v>4.721074219560251e-05</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.001710825366899371</v>
+        <v>4.664241714635864e-05</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.002068309113383293</v>
+        <v>1.087081182049587e-05</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0004453820001799613</v>
+        <v>2.236322688986547e-05</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0002310526906512678</v>
+        <v>1.892960790428333e-05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0001297011040151119</v>
+        <v>1.416260147379944e-05</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.001772144809365273</v>
+        <v>5.241924736765213e-05</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0005076058441773057</v>
+        <v>4.786717545357533e-05</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0005948789184913039</v>
+        <v>5.743162182625383e-05</v>
       </c>
       <c r="DN14" t="n">
-        <v>7.137792999856174e-05</v>
+        <v>1.433476427337155e-05</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.001346036093309522</v>
+        <v>1.000995234790025e-05</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0009215110912919044</v>
+        <v>2.273634163429961e-05</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0001947935670614243</v>
+        <v>1.602605334483087e-05</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.001768043846823275</v>
+        <v>3.890263542416506e-05</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0008334890007972717</v>
+        <v>1.236525167769287e-05</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0007154096383601427</v>
+        <v>2.231250255135819e-05</v>
       </c>
       <c r="DU14" t="n">
-        <v>3.906944766640663e-05</v>
+        <v>1.757072459440678e-05</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.001289713196456432</v>
+        <v>2.992382542288397e-05</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0003930206003133208</v>
+        <v>6.290668534347787e-05</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.001803657622076571</v>
+        <v>4.141372119192965e-05</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0004864934307988733</v>
+        <v>1.864131263573654e-05</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0003506617795210332</v>
+        <v>1.073169414667063e-06</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0009895735420286655</v>
+        <v>3.583068246371113e-05</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.000986642437055707</v>
+        <v>4.357660873210989e-05</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.693246667855419e-05</v>
+        <v>1.933855492097791e-05</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0004159039235673845</v>
+        <v>3.33259449689649e-05</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0001954190811375156</v>
+        <v>1.937611159519292e-05</v>
       </c>
       <c r="EF14" t="n">
-        <v>7.124655530788004e-05</v>
+        <v>3.124224531347863e-05</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0005429349257610738</v>
+        <v>2.232270344393328e-05</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.001388640492223203</v>
+        <v>1.78974587470293e-05</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.001580947078764439</v>
+        <v>6.751615728717297e-05</v>
       </c>
       <c r="EJ14" t="n">
-        <v>1.106459967559204e-05</v>
+        <v>1.967227763088886e-05</v>
       </c>
       <c r="EK14" t="n">
-        <v>2.320178646186832e-05</v>
+        <v>6.349993782350793e-06</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0005255861324258149</v>
+        <v>1.127610971707327e-06</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0001049562415573746</v>
+        <v>5.117483397043543e-07</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0006203787634149194</v>
+        <v>8.616607374278829e-07</v>
       </c>
       <c r="EO14" t="n">
-        <v>5.860271630808711e-05</v>
+        <v>9.937805316440063e-07</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.001268016174435616</v>
+        <v>2.699035030673258e-05</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0006558119785040617</v>
+        <v>1.911696017486975e-05</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0009180654305964708</v>
+        <v>3.350668339408003e-05</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0006899108993820846</v>
+        <v>1.035020977724344e-05</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.000164582539582625</v>
+        <v>5.737128230975941e-05</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0006550580728799105</v>
+        <v>9.196170140057802e-06</v>
       </c>
       <c r="EV14" t="n">
-        <v>6.432411464629695e-05</v>
+        <v>4.48706814495381e-05</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.000890774535946548</v>
+        <v>1.346644876321079e-05</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.000478508765809238</v>
+        <v>5.372919531509979e-08</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0005411448073573411</v>
+        <v>1.564812191645615e-05</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.001244725310243666</v>
+        <v>4.407982851262204e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0007857878226786852</v>
+        <v>6.431840301956981e-05</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0005293726571835577</v>
+        <v>1.151941614807583e-05</v>
       </c>
       <c r="FC14" t="n">
-        <v>8.86127381818369e-05</v>
+        <v>2.88915507553611e-05</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0004357514262665063</v>
+        <v>4.42221607954707e-06</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0003281071549281478</v>
+        <v>2.301033964613453e-05</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0003445648471824825</v>
+        <v>1.558310577820521e-05</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0001804527564672753</v>
+        <v>1.231563237524824e-05</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0009862004080787301</v>
+        <v>2.701280027395114e-05</v>
       </c>
       <c r="FI14" t="n">
-        <v>1.843195059336722e-05</v>
+        <v>1.319254261034075e-05</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0007936906768009067</v>
+        <v>3.103630660916679e-05</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0003930855600629002</v>
+        <v>2.504929943825118e-05</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0006974975694902241</v>
+        <v>3.990684490418062e-05</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.0004099537909496576</v>
+        <v>9.57827978709247e-07</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0007143021794036031</v>
+        <v>7.907328836154193e-06</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0004432220885064453</v>
+        <v>2.498629783076467e-06</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0009679358918219805</v>
+        <v>9.551218681735918e-05</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0006970454705879092</v>
+        <v>5.85437192057725e-06</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.00137997476849705</v>
+        <v>2.610628143884242e-05</v>
       </c>
       <c r="FS14" t="n">
-        <v>6.945949280634522e-05</v>
+        <v>1.573615372763015e-05</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0002660626778379083</v>
+        <v>6.239503272809088e-05</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0006493350374512374</v>
+        <v>3.825252497335896e-05</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001854190195444971</v>
+        <v>4.353907570475712e-05</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.000627756176982075</v>
+        <v>3.767885209526867e-05</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0003389260964468122</v>
+        <v>2.243151175207458e-05</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.0002946047170553356</v>
+        <v>3.237400960642844e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0009633840527385473</v>
+        <v>2.060984661511611e-05</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0002214991836808622</v>
+        <v>1.302203781960998e-05</v>
       </c>
       <c r="GB14" t="n">
-        <v>8.677876758156344e-05</v>
+        <v>6.570178811671212e-05</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.001028981292620301</v>
+        <v>1.768547190295067e-05</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.001545144594274461</v>
+        <v>3.656259286799468e-05</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0006669668946415186</v>
+        <v>8.579567293054424e-06</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0001164838613476604</v>
+        <v>2.608295835671015e-05</v>
       </c>
       <c r="GG14" t="n">
-        <v>4.945537511957809e-06</v>
+        <v>4.520147922448814e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.144135239883326e-06</v>
+        <v>3.63124163413886e-05</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0004247194156050682</v>
+        <v>0.0002725191006902605</v>
       </c>
       <c r="C15" t="n">
-        <v>7.887799438321963e-05</v>
+        <v>5.17314656462986e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001762864267220721</v>
+        <v>0.0001412053825333714</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0002668102097231895</v>
+        <v>3.825221938313916e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0002014251949731261</v>
+        <v>0.000202748051378876</v>
       </c>
       <c r="G15" t="n">
-        <v>7.921770156826824e-05</v>
+        <v>3.258468495914713e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0001100318477256224</v>
+        <v>0.0001622035197215155</v>
       </c>
       <c r="I15" t="n">
-        <v>3.230910078855231e-05</v>
+        <v>1.504520696471445e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>4.903999069938436e-06</v>
+        <v>8.397846977459267e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0003251529997214675</v>
+        <v>0.0003807085449807346</v>
       </c>
       <c r="L15" t="n">
-        <v>1.79852268047398e-05</v>
+        <v>3.185319656040519e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0001134737831307575</v>
+        <v>0.0002266443334519863</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0002079705009236932</v>
+        <v>0.0001418286265106872</v>
       </c>
       <c r="O15" t="n">
-        <v>0.000195918430108577</v>
+        <v>0.0001983224356081337</v>
       </c>
       <c r="P15" t="n">
-        <v>8.533387881470844e-05</v>
+        <v>7.884683145675808e-05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.492478779458907e-05</v>
+        <v>5.199751831241883e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>3.629837738117203e-05</v>
+        <v>5.210960807744414e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>5.730226348532597e-06</v>
+        <v>4.488425474846736e-05</v>
       </c>
       <c r="T15" t="n">
-        <v>7.144099799916148e-05</v>
+        <v>2.774319182208274e-05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.009912466543028e-05</v>
+        <v>3.68037581210956e-05</v>
       </c>
       <c r="V15" t="n">
-        <v>5.840662197442725e-05</v>
+        <v>1.559987140353769e-05</v>
       </c>
       <c r="W15" t="n">
-        <v>4.903901208308525e-05</v>
+        <v>4.856502073380398e-06</v>
       </c>
       <c r="X15" t="n">
-        <v>7.049219129839912e-05</v>
+        <v>1.862282988440711e-05</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.532710823288653e-05</v>
+        <v>4.26326078013517e-05</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.281628182274289e-05</v>
+        <v>3.37284327542875e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.047526479349472e-05</v>
+        <v>2.66461956925923e-05</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.558073174441233e-05</v>
+        <v>6.343134009512141e-05</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.261312228161842e-05</v>
+        <v>7.611150795128196e-05</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.156281415314879e-06</v>
+        <v>2.001460597966798e-05</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.432932135183364e-05</v>
+        <v>3.043211108888499e-05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.523613173048943e-05</v>
+        <v>7.434921280946583e-05</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.100556932622567e-05</v>
+        <v>7.722813279542606e-06</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.043735680170357e-05</v>
+        <v>1.580261596245691e-05</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.865081427851692e-05</v>
+        <v>6.489341467386112e-05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6.238335117814131e-06</v>
+        <v>2.136983857781161e-05</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.912545096478425e-05</v>
+        <v>4.114941475563683e-06</v>
       </c>
       <c r="AL15" t="n">
-        <v>9.378769755130634e-05</v>
+        <v>7.224393357319059e-06</v>
       </c>
       <c r="AM15" t="n">
-        <v>5.720271474274341e-07</v>
+        <v>2.782584851956926e-05</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.580961907166056e-05</v>
+        <v>2.030483301496133e-07</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.023613913275767e-05</v>
+        <v>5.895632784813643e-05</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.488536357413977e-05</v>
+        <v>5.179374420549721e-05</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.346679245121777e-06</v>
+        <v>5.754547601100057e-05</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.950765676563606e-05</v>
+        <v>9.281172970077023e-05</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.432847345015034e-05</v>
+        <v>2.74588746833615e-05</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.860055221593939e-05</v>
+        <v>5.368485653889365e-05</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.0002843094698619097</v>
+        <v>0.0002831870515365154</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.668456651619636e-05</v>
+        <v>2.365178261243273e-05</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.238945282646455e-05</v>
+        <v>5.463738852995448e-05</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0001121462701121345</v>
+        <v>0.0001261731958948076</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.0001403058122377843</v>
+        <v>0.0001426147646270692</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.395013259752886e-05</v>
+        <v>5.270866495266091e-06</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.867064803373069e-05</v>
+        <v>4.07315701522748e-06</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.621017145225778e-05</v>
+        <v>4.406046355143189e-05</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03069451142801e-05</v>
+        <v>4.456502210814506e-05</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.203295197337866e-05</v>
+        <v>4.241568967700005e-05</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.039233994670212e-05</v>
+        <v>2.851468343578745e-05</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.840794958407059e-05</v>
+        <v>5.039842653786764e-05</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.0001745302579365671</v>
+        <v>2.584327739896253e-05</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.390792699065059e-05</v>
+        <v>4.141472891205922e-05</v>
       </c>
       <c r="BI15" t="n">
-        <v>7.056917092995718e-05</v>
+        <v>2.240728827018756e-05</v>
       </c>
       <c r="BJ15" t="n">
-        <v>5.555052484851331e-05</v>
+        <v>0.0001293172826990485</v>
       </c>
       <c r="BK15" t="n">
-        <v>2.519765257602558e-05</v>
+        <v>3.086451761191711e-05</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.958340180863161e-05</v>
+        <v>4.935203469358385e-05</v>
       </c>
       <c r="BM15" t="n">
-        <v>7.574875780846924e-05</v>
+        <v>6.439255230361596e-05</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.345184788689949e-05</v>
+        <v>8.631154742033686e-06</v>
       </c>
       <c r="BO15" t="n">
-        <v>7.98931341705611e-06</v>
+        <v>6.380352715495974e-05</v>
       </c>
       <c r="BP15" t="n">
-        <v>1.117483225243632e-05</v>
+        <v>9.486398630542681e-05</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.080290818819776e-05</v>
+        <v>1.679992237768602e-05</v>
       </c>
       <c r="BR15" t="n">
-        <v>2.644135565788019e-05</v>
+        <v>4.68653452116996e-05</v>
       </c>
       <c r="BS15" t="n">
-        <v>2.551536999817472e-05</v>
+        <v>2.878445047826972e-05</v>
       </c>
       <c r="BT15" t="n">
-        <v>2.978403608722147e-05</v>
+        <v>2.308065086253919e-05</v>
       </c>
       <c r="BU15" t="n">
-        <v>3.429173011681996e-05</v>
+        <v>3.964411007473245e-05</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0001781567989382893</v>
+        <v>0.0001209993206430227</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.935660636983812e-05</v>
+        <v>1.226399217557628e-05</v>
       </c>
       <c r="BX15" t="n">
-        <v>4.173601701040752e-05</v>
+        <v>3.323513737996109e-05</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.465222734026611e-05</v>
+        <v>1.606497244210914e-05</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.337911271548364e-05</v>
+        <v>3.154194564558566e-05</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.794016679923516e-05</v>
+        <v>5.627037899103016e-05</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.296260026923846e-05</v>
+        <v>3.45101288985461e-05</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.960658093797974e-05</v>
+        <v>2.783268610073719e-05</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.632517629943322e-06</v>
+        <v>9.216394573741127e-06</v>
       </c>
       <c r="CE15" t="n">
-        <v>6.798426329623908e-05</v>
+        <v>6.830296479165554e-05</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.290404336235952e-05</v>
+        <v>1.572703513375018e-05</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.283534533693455e-05</v>
+        <v>1.495747710578144e-05</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.318295107921585e-05</v>
+        <v>2.660612517502159e-05</v>
       </c>
       <c r="CI15" t="n">
-        <v>4.231419006828219e-05</v>
+        <v>3.627585829235613e-05</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.810072353691794e-05</v>
+        <v>2.639157173689455e-06</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.234005048900144e-05</v>
+        <v>7.320059921767097e-06</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.548458749311976e-05</v>
+        <v>4.70189843326807e-06</v>
       </c>
       <c r="CM15" t="n">
-        <v>6.054488767404109e-05</v>
+        <v>3.693684266181663e-05</v>
       </c>
       <c r="CN15" t="n">
-        <v>3.751268195628654e-06</v>
+        <v>0.0001503330277046189</v>
       </c>
       <c r="CO15" t="n">
-        <v>7.382400326605421e-06</v>
+        <v>5.447008152259514e-05</v>
       </c>
       <c r="CP15" t="n">
-        <v>5.312388566380832e-06</v>
+        <v>7.125046522560297e-06</v>
       </c>
       <c r="CQ15" t="n">
-        <v>1.156754115072545e-05</v>
+        <v>3.55357497028308e-06</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.97346817003563e-05</v>
+        <v>7.15224723535357e-06</v>
       </c>
       <c r="CS15" t="n">
-        <v>7.367920625256374e-05</v>
+        <v>1.093632090487517e-05</v>
       </c>
       <c r="CT15" t="n">
-        <v>6.404734449461102e-05</v>
+        <v>2.1707692212658e-06</v>
       </c>
       <c r="CU15" t="n">
-        <v>3.776762241614051e-06</v>
+        <v>8.240514944191091e-06</v>
       </c>
       <c r="CV15" t="n">
-        <v>4.697745680459775e-06</v>
+        <v>2.34539074881468e-05</v>
       </c>
       <c r="CW15" t="n">
-        <v>5.333154331310652e-05</v>
+        <v>7.765858754282817e-05</v>
       </c>
       <c r="CX15" t="n">
-        <v>2.93856155622052e-05</v>
+        <v>1.254289145435905e-05</v>
       </c>
       <c r="CY15" t="n">
-        <v>4.764420737046748e-05</v>
+        <v>2.440924072288908e-05</v>
       </c>
       <c r="CZ15" t="n">
-        <v>7.632856068084948e-06</v>
+        <v>6.516406756418291e-07</v>
       </c>
       <c r="DA15" t="n">
-        <v>5.718956163036637e-05</v>
+        <v>4.498089401749894e-05</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.258692827832419e-05</v>
+        <v>1.783746120054275e-05</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.102286089211702e-05</v>
+        <v>1.955941115738824e-07</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.320259798376355e-06</v>
+        <v>9.522091204416938e-06</v>
       </c>
       <c r="DE15" t="n">
-        <v>3.214063326595351e-05</v>
+        <v>1.385536324960412e-05</v>
       </c>
       <c r="DF15" t="n">
-        <v>9.27834480535239e-05</v>
+        <v>6.866813055239618e-05</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.101228735933546e-05</v>
+        <v>0.0001359833695460111</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0001012304710457101</v>
+        <v>4.202255149721168e-05</v>
       </c>
       <c r="DI15" t="n">
-        <v>2.892127122322563e-05</v>
+        <v>2.778623456833884e-05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>6.17704245087225e-06</v>
+        <v>8.506569429300725e-05</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.045502959750593e-05</v>
+        <v>2.085049709421583e-05</v>
       </c>
       <c r="DL15" t="n">
-        <v>4.192654159851372e-05</v>
+        <v>1.106915442505851e-05</v>
       </c>
       <c r="DM15" t="n">
-        <v>4.302990782889538e-05</v>
+        <v>3.457580532995053e-06</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.302293094340712e-05</v>
+        <v>1.188653550343588e-05</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.453538218105678e-05</v>
+        <v>7.63641728553921e-05</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.925667316361796e-06</v>
+        <v>1.697210450402054e-06</v>
       </c>
       <c r="DQ15" t="n">
-        <v>4.688721674028784e-05</v>
+        <v>5.860400415258482e-05</v>
       </c>
       <c r="DR15" t="n">
-        <v>1.532076930743642e-05</v>
+        <v>2.885762296500616e-05</v>
       </c>
       <c r="DS15" t="n">
-        <v>6.038781066308729e-05</v>
+        <v>3.851549263345078e-05</v>
       </c>
       <c r="DT15" t="n">
-        <v>2.541182402637787e-05</v>
+        <v>3.701923560583964e-06</v>
       </c>
       <c r="DU15" t="n">
-        <v>2.316040263394825e-05</v>
+        <v>1.068520396074746e-05</v>
       </c>
       <c r="DV15" t="n">
-        <v>1.588164559507277e-05</v>
+        <v>4.298023122828454e-05</v>
       </c>
       <c r="DW15" t="n">
-        <v>3.489976734272204e-07</v>
+        <v>4.029432602692395e-05</v>
       </c>
       <c r="DX15" t="n">
-        <v>6.429270797525533e-06</v>
+        <v>3.295393253210932e-05</v>
       </c>
       <c r="DY15" t="n">
-        <v>4.353262920631096e-05</v>
+        <v>5.48143834748771e-05</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.035277819028124e-06</v>
+        <v>1.723365312500391e-05</v>
       </c>
       <c r="EA15" t="n">
-        <v>2.992536064994056e-05</v>
+        <v>3.853856105706654e-05</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.609467628644779e-05</v>
+        <v>3.91878311347682e-05</v>
       </c>
       <c r="EC15" t="n">
-        <v>4.011549208371434e-07</v>
+        <v>1.982237699849065e-05</v>
       </c>
       <c r="ED15" t="n">
-        <v>4.052298027090728e-05</v>
+        <v>7.827499211998656e-05</v>
       </c>
       <c r="EE15" t="n">
-        <v>1.364006857329514e-05</v>
+        <v>4.791744868271053e-05</v>
       </c>
       <c r="EF15" t="n">
-        <v>3.874164758599363e-05</v>
+        <v>2.951399437733926e-05</v>
       </c>
       <c r="EG15" t="n">
-        <v>4.769870429299772e-05</v>
+        <v>1.129600696003763e-05</v>
       </c>
       <c r="EH15" t="n">
-        <v>3.558797834557481e-05</v>
+        <v>6.735713213856798e-06</v>
       </c>
       <c r="EI15" t="n">
-        <v>2.14052852243185e-05</v>
+        <v>9.659576608100906e-05</v>
       </c>
       <c r="EJ15" t="n">
-        <v>3.240238584112376e-05</v>
+        <v>2.441835385980085e-05</v>
       </c>
       <c r="EK15" t="n">
-        <v>2.380908335908316e-05</v>
+        <v>4.958789577358402e-05</v>
       </c>
       <c r="EL15" t="n">
-        <v>2.731058157223742e-05</v>
+        <v>2.872927780117607e-06</v>
       </c>
       <c r="EM15" t="n">
-        <v>6.386806035152404e-06</v>
+        <v>2.503365431039128e-05</v>
       </c>
       <c r="EN15" t="n">
-        <v>4.326419457356678e-06</v>
+        <v>8.176322808139957e-06</v>
       </c>
       <c r="EO15" t="n">
-        <v>1.584657002240419e-05</v>
+        <v>5.420714660431258e-05</v>
       </c>
       <c r="EP15" t="n">
-        <v>1.795933167159092e-05</v>
+        <v>2.244024653919041e-05</v>
       </c>
       <c r="EQ15" t="n">
-        <v>5.692361446563154e-05</v>
+        <v>1.509353478468256e-05</v>
       </c>
       <c r="ER15" t="n">
-        <v>4.621267362381332e-05</v>
+        <v>1.94826461665798e-05</v>
       </c>
       <c r="ES15" t="n">
-        <v>2.351759030716494e-05</v>
+        <v>3.220081634935923e-05</v>
       </c>
       <c r="ET15" t="n">
-        <v>5.046898877480999e-05</v>
+        <v>7.085434390319278e-06</v>
       </c>
       <c r="EU15" t="n">
-        <v>2.057822894130368e-05</v>
+        <v>2.979701639560517e-05</v>
       </c>
       <c r="EV15" t="n">
-        <v>5.251662514638156e-05</v>
+        <v>1.188883470604196e-05</v>
       </c>
       <c r="EW15" t="n">
-        <v>8.05621766630793e-06</v>
+        <v>2.851954832294723e-06</v>
       </c>
       <c r="EX15" t="n">
-        <v>1.222914397658315e-05</v>
+        <v>9.010096619022079e-06</v>
       </c>
       <c r="EY15" t="n">
-        <v>5.13975573994685e-05</v>
+        <v>8.253561827586964e-05</v>
       </c>
       <c r="EZ15" t="n">
-        <v>1.757462450768799e-05</v>
+        <v>2.183395736210514e-05</v>
       </c>
       <c r="FA15" t="n">
-        <v>4.595228892867453e-05</v>
+        <v>1.105790943256579e-05</v>
       </c>
       <c r="FB15" t="n">
-        <v>5.230128863331629e-07</v>
+        <v>6.494418357760878e-06</v>
       </c>
       <c r="FC15" t="n">
-        <v>4.850561526836827e-05</v>
+        <v>3.3922704460565e-05</v>
       </c>
       <c r="FD15" t="n">
-        <v>2.605691952339839e-05</v>
+        <v>2.059223334072158e-07</v>
       </c>
       <c r="FE15" t="n">
-        <v>2.199413574999198e-05</v>
+        <v>6.729537744831759e-06</v>
       </c>
       <c r="FF15" t="n">
-        <v>2.035747093032114e-05</v>
+        <v>9.640489224693738e-06</v>
       </c>
       <c r="FG15" t="n">
-        <v>4.808925950783305e-06</v>
+        <v>1.736001468088944e-05</v>
       </c>
       <c r="FH15" t="n">
-        <v>3.958619345212355e-05</v>
+        <v>3.039241346414201e-05</v>
       </c>
       <c r="FI15" t="n">
-        <v>3.748705057660118e-05</v>
+        <v>9.561003935232293e-06</v>
       </c>
       <c r="FJ15" t="n">
-        <v>5.647804937325418e-05</v>
+        <v>1.895962122944184e-05</v>
       </c>
       <c r="FK15" t="n">
-        <v>1.697178959148005e-05</v>
+        <v>6.301593384705484e-05</v>
       </c>
       <c r="FL15" t="n">
-        <v>3.938442750950344e-05</v>
+        <v>4.136168172408361e-06</v>
       </c>
       <c r="FM15" t="n">
-        <v>1.942671406141017e-05</v>
+        <v>3.310521424282342e-05</v>
       </c>
       <c r="FN15" t="n">
-        <v>3.218322672182694e-05</v>
+        <v>2.888574726966908e-06</v>
       </c>
       <c r="FO15" t="n">
-        <v>3.869440843118355e-05</v>
+        <v>7.159221422625706e-05</v>
       </c>
       <c r="FP15" t="n">
-        <v>2.173497159674298e-05</v>
+        <v>4.293422898626886e-05</v>
       </c>
       <c r="FQ15" t="n">
-        <v>4.738073403132148e-05</v>
+        <v>1.241150948771974e-05</v>
       </c>
       <c r="FR15" t="n">
-        <v>2.161208794859704e-05</v>
+        <v>3.95922725147102e-05</v>
       </c>
       <c r="FS15" t="n">
-        <v>8.37217885418795e-05</v>
+        <v>0.0001072358354576863</v>
       </c>
       <c r="FT15" t="n">
-        <v>6.472474342444912e-05</v>
+        <v>7.670700142625719e-05</v>
       </c>
       <c r="FU15" t="n">
-        <v>9.408029654878192e-06</v>
+        <v>9.911431698128581e-05</v>
       </c>
       <c r="FV15" t="n">
-        <v>2.89709132630378e-05</v>
+        <v>8.754341979511082e-05</v>
       </c>
       <c r="FW15" t="n">
-        <v>2.791450606309809e-05</v>
+        <v>9.835512901190668e-05</v>
       </c>
       <c r="FX15" t="n">
-        <v>1.119237640523352e-05</v>
+        <v>7.555383945145877e-06</v>
       </c>
       <c r="FY15" t="n">
-        <v>5.820060323458165e-05</v>
+        <v>2.807609598676208e-05</v>
       </c>
       <c r="FZ15" t="n">
-        <v>7.917844868643442e-07</v>
+        <v>7.449894837918691e-06</v>
       </c>
       <c r="GA15" t="n">
-        <v>2.4302191377501e-05</v>
+        <v>2.707145540625788e-06</v>
       </c>
       <c r="GB15" t="n">
-        <v>4.577270374284126e-05</v>
+        <v>2.78480292763561e-05</v>
       </c>
       <c r="GC15" t="n">
-        <v>4.58371068816632e-05</v>
+        <v>1.674211853242014e-05</v>
       </c>
       <c r="GD15" t="n">
-        <v>5.692778358934447e-05</v>
+        <v>3.782503699767403e-05</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.0001493427553214133</v>
+        <v>4.828255987376906e-05</v>
       </c>
       <c r="GF15" t="n">
-        <v>1.021136267809197e-05</v>
+        <v>1.276537568628555e-05</v>
       </c>
       <c r="GG15" t="n">
-        <v>2.052039235422853e-05</v>
+        <v>2.568702620919794e-05</v>
       </c>
     </row>
     <row r="16">
